--- a/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
@@ -732,1814 +732,1814 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.07145902724062485</v>
+        <v>-0.0100777373946481</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.02467418576065321</v>
+        <v>0.0002611490568513757</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1808287525325419</v>
+        <v>3.588467043203067e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01652073721529905</v>
+        <v>0.0845163267885278</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07325373263734752</v>
+        <v>0.04409236589353237</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2185531237610392</v>
+        <v>-0.01241980387588445</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08102678819733337</v>
+        <v>0.1278599899058752</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07932538394759972</v>
+        <v>-0.1079323142862748</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0395112696361694</v>
+        <v>-2.258303372821985e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06136334131745402</v>
+        <v>0.1918880320889485</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0523695268416343</v>
+        <v>-0.1483640259096808</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1174103447337989</v>
+        <v>0.1013467984451662</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1869618611272174</v>
+        <v>0.2545420056317152</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06207431966749683</v>
+        <v>0.180360172011658</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2366730209504129</v>
+        <v>-0.1285582344944099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07497379708254118</v>
+        <v>0.2705035498389899</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03790891056063166</v>
+        <v>-0.02108352715813281</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1484901769031669</v>
+        <v>0.001123488091381433</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09503704011914318</v>
+        <v>-0.1064882104407642</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07341433890650507</v>
+        <v>0.0442450459374919</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2040654420109548</v>
+        <v>-0.01606931579525504</v>
       </c>
       <c r="V2" t="n">
-        <v>0.214874317526783</v>
+        <v>-0.1381212043437244</v>
       </c>
       <c r="W2" t="n">
-        <v>-9.880481809570731e-07</v>
+        <v>-0.02977139623942329</v>
       </c>
       <c r="X2" t="n">
-        <v>0.07161231971516456</v>
+        <v>0.02169283238441352</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1407676951002871</v>
+        <v>0.1927955048552167</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.007590481617192182</v>
+        <v>0.01976931776211168</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03815529105681723</v>
+        <v>-0.07609981839734863</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2400074759278107</v>
+        <v>3.753016565849269e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2077051037888419</v>
+        <v>0.05072327981303794</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1271021105110575</v>
+        <v>0.2023042593651587</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02588046119962946</v>
+        <v>0.205324892762822</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1065341148314166</v>
+        <v>0.182744966255898</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0008061401687837193</v>
+        <v>-5.483838776901589e-07</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.02666347885897557</v>
+        <v>-0.2098218207357924</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.04585523098794193</v>
+        <v>-0.2368706144278402</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001630140239081724</v>
+        <v>-0.1755351823377795</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.1506309879824927</v>
+        <v>3.502513498578456e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2694373355008042</v>
+        <v>-0.08405314373093732</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.18940052943041</v>
+        <v>-0.09276499410618992</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.1137652459023097</v>
+        <v>0.000499674985468305</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1385730475248231</v>
+        <v>-0.1176434549958445</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.09402035453438656</v>
+        <v>0.03335381676007687</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.1590098501450641</v>
+        <v>-0.04712343965211781</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.05098927454826618</v>
+        <v>-0.0008939854611719594</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.01973129711553788</v>
+        <v>-0.1829533176177319</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.2074989789268961</v>
+        <v>0.02903855565113455</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.05657208394445887</v>
+        <v>-0.1406009945277586</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1773821051151033</v>
+        <v>1.224663393263067e-09</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.06590761547828518</v>
+        <v>-0.005939369686492252</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05036428897516639</v>
+        <v>-0.187708311967764</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.07756493306715492</v>
+        <v>0.2285666972898632</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2189715368050978</v>
+        <v>0.01234355513533185</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.04165227845067714</v>
+        <v>0.1674111496147841</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.004288500244063689</v>
+        <v>0.005711689948774746</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.05491906722469491</v>
+        <v>0.006455410696953328</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.2160068002868417</v>
+        <v>-0.06231850684046125</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.2471531118498854</v>
+        <v>0.2037015423404008</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.03037199763133362</v>
+        <v>-0.1310029442328044</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03902928570867122</v>
+        <v>-0.09131623177981425</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.06993953353106278</v>
+        <v>0.1995267976559436</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.03207506005881351</v>
+        <v>-0.07176185228958198</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.04066184273863688</v>
+        <v>0.1235408020742824</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.2063166334440907</v>
+        <v>-0.005018741545351506</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.2595034259628292</v>
+        <v>0.06943078684244844</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01819571475391809</v>
+        <v>0.005627566805453265</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01738081934628345</v>
+        <v>0.1669338144158722</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.1939758128085066</v>
+        <v>0.07715965750681182</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0834516662654347</v>
+        <v>-0.2029959676356316</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.08753742343351276</v>
+        <v>0.203875810633749</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.08057014601366259</v>
+        <v>-0.1964863765168867</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.01399541130899473</v>
+        <v>0.003425925395437803</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.1787033279379146</v>
+        <v>0.005004944306798741</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.05417791084142373</v>
+        <v>-0.02214484593133721</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2240772194020823</v>
+        <v>-0.1517685784034685</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.1420659454609353</v>
+        <v>-0.2211334802992808</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.02161361482762544</v>
+        <v>-0.04510580138335059</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1022691522922957</v>
+        <v>0.1391405099039476</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.2392912794870293</v>
+        <v>-0.1875193452647843</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1276991350255993</v>
+        <v>-0.02967669409524809</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.2184634912898641</v>
+        <v>0.230799518790217</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.09390512517893937</v>
+        <v>-2.644447479230682e-08</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0959681803279574</v>
+        <v>0.0002362615276252102</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1266486280163158</v>
+        <v>-0.1586892409307296</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.0002058581221277311</v>
+        <v>0.08103173382136092</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.2505334969755139</v>
+        <v>-0.2086272446373512</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.01797096440382455</v>
+        <v>0.07784262046928017</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.03338990380614826</v>
+        <v>-0.1320578529034222</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0.1782933272269011</v>
+        <v>-0.1619176139700363</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.06190854292795176</v>
+        <v>1.071902672675909e-10</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.09745482455926641</v>
+        <v>0.186982152430455</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1407780693935203</v>
+        <v>0.006012252468416446</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.003653302092113541</v>
+        <v>-0.2052141815452515</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1467290366514301</v>
+        <v>-0.0007288607384794353</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.2102582053431621</v>
+        <v>-0.1823305856055239</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-7.255565189959643e-07</v>
+        <v>-0.1355872468447399</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.02024978569777658</v>
+        <v>-0.1756401051607913</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.02193522886776725</v>
+        <v>0.06082698203071486</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.0123853394691414</v>
+        <v>-0.1467181359187702</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.1411336395877845</v>
+        <v>-0.1049744861794819</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.1892031720344466</v>
+        <v>-0.01023537723573164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.008559579557334777</v>
+        <v>-0.0243760660932431</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1116562794453231</v>
+        <v>-0.1926660158130944</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1900619027452363</v>
+        <v>-0.004138307677941447</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01902103175575575</v>
+        <v>-0.1178315001274852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08387355768877239</v>
+        <v>-0.03277199406260532</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09813662525028645</v>
+        <v>0.1382079547773834</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.03285434551795634</v>
+        <v>0.131269028892073</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2268576581497823</v>
+        <v>-0.1570996379984181</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1446552806491805</v>
+        <v>-3.273781225431475e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2130696143414572</v>
+        <v>0.2170129864442782</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1543516336754453</v>
+        <v>0.03641661029840765</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1374067993190881</v>
+        <v>0.05005544006271122</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1669438635417756</v>
+        <v>-0.006198663467795782</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.08281854263044648</v>
+        <v>0.05630311146660292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07679757574548444</v>
+        <v>-0.06619394411201843</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.004839685573538286</v>
+        <v>-0.1379987099203453</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.09018391094510532</v>
+        <v>0.0002303195377910126</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1600321863650449</v>
+        <v>-0.0003838373897727128</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1508243271900648</v>
+        <v>-0.1585752543723175</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1769023137134535</v>
+        <v>0.004117678780489795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04606649596929827</v>
+        <v>0.0008254609695767673</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2089046349449193</v>
+        <v>0.1310455407498445</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.05446711018053259</v>
+        <v>0.08205727289286767</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1362748384162694</v>
+        <v>-0.224003604476614</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1431509623368958</v>
+        <v>-0.09799183355951938</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.03061983848069041</v>
+        <v>0.01767971033843684</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1254832851813188</v>
+        <v>-0.2198006408809138</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1690649581614405</v>
+        <v>-0.02111594699963395</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.07910688928579253</v>
+        <v>-0.1178210712282283</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1323916034968908</v>
+        <v>-0.08974189542576794</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1352398654764114</v>
+        <v>-0.06832818955964509</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2191403000583982</v>
+        <v>0.2354655639675341</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.06066361465422994</v>
+        <v>-0.006140068442158103</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.03581654493034071</v>
+        <v>0.09323340383782544</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.01879478179959134</v>
+        <v>0.2160845761034486</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0006076550992746949</v>
+        <v>0.07847808004637785</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.04321352169748131</v>
+        <v>-0.01018471894234884</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01179028269013573</v>
+        <v>0.2205133179767585</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.02644170898552142</v>
+        <v>-0.05781704335718713</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1894667552245673</v>
+        <v>-0.01240569741292299</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1653694627105622</v>
+        <v>0.05568328990896248</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.05486033776614039</v>
+        <v>-0.03273562768971706</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1031051120623809</v>
+        <v>0.2404505869372031</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.2208094210162634</v>
+        <v>0.02149050845031608</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.06477988490195005</v>
+        <v>0.1831031751092731</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.09840603893298941</v>
+        <v>0.217881528863039</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1585239924972278</v>
+        <v>-0.0191459924811852</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.03509218758078401</v>
+        <v>-0.01438829635301897</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.05925434263191897</v>
+        <v>0.08173232770322314</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0001984937849724907</v>
+        <v>-0.213189742082947</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.003387495449028111</v>
+        <v>-0.07417451564038897</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0963170391756803</v>
+        <v>-0.01675396843516716</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.2247382968526552</v>
+        <v>0.198798814416085</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.02846556277054013</v>
+        <v>0.2036470617562921</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1214464491417133</v>
+        <v>-0.01742431312698485</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.2165667400251791</v>
+        <v>-0.137379661288222</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.05156037352251849</v>
+        <v>0.2000860465509342</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.07977740683869444</v>
+        <v>0.06407103092483099</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.905073198973686e-06</v>
+        <v>0.09329429868710225</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.005277935184050818</v>
+        <v>0.1676265673807719</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.04547904934046246</v>
+        <v>0.0620637239738225</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.05610054428125803</v>
+        <v>0.07354716643392284</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.05310269178646104</v>
+        <v>-0.008893073723788666</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.01429329571172683</v>
+        <v>0.1138137960371383</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.03162189384977724</v>
+        <v>-0.0132472887023793</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.05890804077424839</v>
+        <v>-0.0281906460874927</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1120400127122615</v>
+        <v>0.03511482127588324</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.03440486227372934</v>
+        <v>0.1224271736597198</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1991254974263202</v>
+        <v>-0.02242371675886514</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1668186980423584</v>
+        <v>0.2211304990320193</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.09485583396608281</v>
+        <v>-3.970995835467419e-09</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1002976472592697</v>
+        <v>-0.191635380789938</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.00540351541506257</v>
+        <v>-0.00417697579844268</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1703593409627856</v>
+        <v>-0.09783940930156271</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.08178124552037427</v>
+        <v>-0.1839179250458111</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1730247521826112</v>
+        <v>0.09931031877151396</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.02038218817402541</v>
+        <v>0.2214255248817569</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.04667782544136619</v>
+        <v>-0.03051974118994675</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.06868978142693891</v>
+        <v>-0.003160941291248043</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0780489393776724</v>
+        <v>0.07117773932538626</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.01983689709700544</v>
+        <v>-0.006627881877736519</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.07883950895873024</v>
+        <v>-0.01171027094525793</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1807688570267031</v>
+        <v>-0.1596261568063791</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.1819745781380286</v>
+        <v>-0.1240059328348251</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1466251452479883</v>
+        <v>0.173138504745595</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.005239364001484075</v>
+        <v>0.04609793955728853</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.06411219708928728</v>
+        <v>-0.1039120596991157</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1043043807377364</v>
+        <v>0.1880316759957957</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0522786050728907</v>
+        <v>-0.0007426996758293498</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.09470071297378098</v>
+        <v>0.01650102593414619</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.02385618595830637</v>
+        <v>-0.001468888222168598</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.02330419428603902</v>
+        <v>0.1437304709707952</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.05246173518393189</v>
+        <v>-0.0001209263226468192</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.01306553543385867</v>
+        <v>0.1507188518613406</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.04315977400538582</v>
+        <v>0.1591773742647429</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001916238193116795</v>
+        <v>-0.2030355359256676</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.09491745171685458</v>
+        <v>-0.02109729942492018</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1325837869680712</v>
+        <v>0.09425493857725191</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.07460171744226299</v>
+        <v>0.1064736358472799</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.1118360179777416</v>
+        <v>-0.2235396019304792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.03730813304917983</v>
+        <v>-0.02757969927237838</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02139950555170269</v>
+        <v>-0.2314037231233215</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03727654426230541</v>
+        <v>-0.0003967618830383748</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1872311229844573</v>
+        <v>0.1686493691129793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2472348765104471</v>
+        <v>-0.04727346007223469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08399288858974616</v>
+        <v>-0.09615708195230668</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1641434062474175</v>
+        <v>-0.07564574081704679</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03644605142206484</v>
+        <v>0.08928189646370627</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03852492486455254</v>
+        <v>-0.0006218762106009092</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05775090719970919</v>
+        <v>0.1737543400003882</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1854063424806934</v>
+        <v>0.1758429285981551</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07765532208290148</v>
+        <v>-0.009750779013789302</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2269064880888423</v>
+        <v>0.0694345751720658</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03494218392222904</v>
+        <v>-0.01516343154911078</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2234340040668307</v>
+        <v>0.2254473535351857</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01180618491833728</v>
+        <v>0.2431554541547989</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06613991693468949</v>
+        <v>0.1170200491359288</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2247713153497647</v>
+        <v>-0.004215126348508353</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1547129240295539</v>
+        <v>0.2239392930785137</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2385596801540026</v>
+        <v>-0.07687212453421768</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.01707464229161678</v>
+        <v>0.1074119301659689</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2386879913635583</v>
+        <v>0.1956272489977672</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0518128013761386</v>
+        <v>-0.008954241917425004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03089739644398417</v>
+        <v>0.1049710200784925</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.2490999082032968</v>
+        <v>-0.04258380992542456</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.09931451796601483</v>
+        <v>-0.1545576006969112</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.2462010205076291</v>
+        <v>0.2156299218754159</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2208796739914121</v>
+        <v>-0.01841173564884781</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2304410246843392</v>
+        <v>0.1082999753200555</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2288208281903363</v>
+        <v>0.2315369074497849</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.03084981467922597</v>
+        <v>0.2249334700735044</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1886357778814056</v>
+        <v>-0.1275356950954361</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.01512281044652723</v>
+        <v>-0.1665157610876005</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1853500590376082</v>
+        <v>-0.03199302104644162</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.07652281876269112</v>
+        <v>0.1819802494206454</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1554955400297826</v>
+        <v>-0.2302070010680962</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01810951516647941</v>
+        <v>-0.01441589513667496</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04631044457854368</v>
+        <v>0.1775099312366429</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2201683002791772</v>
+        <v>-0.08812902941066621</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1472340429804516</v>
+        <v>-0.06236518848401036</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1991250966533544</v>
+        <v>-0.1528675008972045</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08666011393609965</v>
+        <v>-4.254452614534407e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0898866060046353</v>
+        <v>0.001584810723238469</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.2220967984486103</v>
+        <v>-0.07621445099512332</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.0006987772932252131</v>
+        <v>0.212605856277305</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.09283276333948488</v>
+        <v>0.157449229852237</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.2286532756659051</v>
+        <v>0.1607621761821132</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.126183977754872</v>
+        <v>-0.00151938292313805</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04697936658706479</v>
+        <v>-0.1829449584513241</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.02188702841868303</v>
+        <v>0.009691674394021191</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.04426462716374892</v>
+        <v>0.1580107366750233</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.03185916451849888</v>
+        <v>-0.001676901445505775</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01605270306461395</v>
+        <v>0.1979319692608522</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.01116929942681738</v>
+        <v>0.03973481995684146</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.09150940374109932</v>
+        <v>-3.486004140108568e-11</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1236091274140475</v>
+        <v>-0.1776565459330303</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.07222965942771069</v>
+        <v>0.1246848176963441</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1288824413206116</v>
+        <v>0.0005029873813741576</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.0205856155629983</v>
+        <v>-0.1245754727290255</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.04200770534919376</v>
+        <v>-0.0858708441214137</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.1807167981031102</v>
+        <v>0.2044242582529439</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.0437282426077423</v>
+        <v>-0.05900976814149644</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.1166072677151467</v>
+        <v>-4.984724237814561e-09</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.02314681434318357</v>
+        <v>0.06452650647725171</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.02651676903884105</v>
+        <v>-0.09274988316627443</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0.002587190826958593</v>
+        <v>0.2041746731738801</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.01524938602148858</v>
+        <v>0.1129208202843112</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1971890854821198</v>
+        <v>-0.03262096700337323</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.153106313580491</v>
+        <v>0.2284979804051837</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.06913355320133774</v>
+        <v>0.1270545345862752</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.03372013720594833</v>
+        <v>-0.01385191208318505</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.2141070870620352</v>
+        <v>0.05653720553214762</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.009371287934703224</v>
+        <v>-1.96799662007476e-11</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01875625667146327</v>
+        <v>0.09042547261640183</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0198191433116499</v>
+        <v>0.02681703273962846</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.03386731986972819</v>
+        <v>-0.1455853688519574</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.04053389375010022</v>
+        <v>-0.2089025384215928</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.119948523387069</v>
+        <v>0.1410379088925134</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0.2043908811483625</v>
+        <v>-0.0002293586367742409</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0.1015139348155448</v>
+        <v>0.08617720928259331</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0.1004285804343568</v>
+        <v>-3.820219207923317e-08</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1952678028329515</v>
+        <v>-0.1617160169007852</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.2069626653154276</v>
+        <v>0.01780729594532531</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.2034873884595171</v>
+        <v>0.1103575952984874</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.03083376245093749</v>
+        <v>0.04238397006647134</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1580368700653753</v>
+        <v>0.2016148250438523</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.2171629608314282</v>
+        <v>0.005971685427632545</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.1765768592147253</v>
+        <v>0.1157110796606582</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.09309698467096428</v>
+        <v>1.898156916354277e-10</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.001859049187772288</v>
+        <v>-0.07312428514040065</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1923410173445821</v>
+        <v>-0.01714968691242642</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.1018923993509853</v>
+        <v>0.1386371627549529</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1564257340867866</v>
+        <v>-2.794317414876946e-06</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1157102728501192</v>
+        <v>0.06543410186112596</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.04295796672882529</v>
+        <v>0.1014767386848307</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.009302859410168021</v>
+        <v>0.213143755898683</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1538755008074364</v>
+        <v>0.1259730430504759</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.1211252455312304</v>
+        <v>-0.1104365416032521</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.1452839832800412</v>
+        <v>-0.1712019086087697</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.0046578184711199</v>
+        <v>0.2361331459881215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-6.084050267380835e-05</v>
+        <v>-0.02157669213709057</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.06931516719298325</v>
+        <v>0.04327525726169842</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.07899336768945199</v>
+        <v>0.000267555634944832</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1054187734568407</v>
+        <v>-0.1494427348111508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2132638502541443</v>
+        <v>0.07669461518150904</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2421713482038945</v>
+        <v>-0.1847145975477987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1615317321579065</v>
+        <v>0.1643592198206955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09122523396071756</v>
+        <v>-0.08266000842821067</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1582648558614982</v>
+        <v>-1.208141857702821e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1484963199497905</v>
+        <v>-0.1594152018221891</v>
       </c>
       <c r="K5" t="n">
-        <v>0.116316121483</v>
+        <v>-0.05028692924552683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.168602843833312</v>
+        <v>0.1479350008703972</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1919617156074935</v>
+        <v>-0.116085537767525</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08208743113573698</v>
+        <v>0.2412275939538686</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.08132313507828157</v>
+        <v>-0.09671769209456971</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002254877047565932</v>
+        <v>-0.1548872557368859</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003241733993472848</v>
+        <v>-0.1055063570489502</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.06031343906470447</v>
+        <v>3.58364544492198e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1435837820218125</v>
+        <v>0.1370837420917866</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1553901671361796</v>
+        <v>0.1346104748888121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1997923450498261</v>
+        <v>0.0236217249271591</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.03310873033003998</v>
+        <v>0.1292572740387446</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.447122254071088e-06</v>
+        <v>0.1245641005714984</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1248374673824243</v>
+        <v>0.1904343120016914</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1236603869247159</v>
+        <v>-0.07473418397563109</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.213373334439494e-06</v>
+        <v>0.04538141671594647</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1433372384830287</v>
+        <v>-0.02417247410404122</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0635252592263266</v>
+        <v>-0.0003446659977204049</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1130020108160393</v>
+        <v>0.1936842563719671</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1681789740655127</v>
+        <v>0.1084237001459652</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2403508590614704</v>
+        <v>0.2307752836427098</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06728546183671225</v>
+        <v>-0.2341908941149027</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.05255020145152035</v>
+        <v>-0.1060763200543335</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.008184175355524338</v>
+        <v>-0.08448256720194276</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06925683670608238</v>
+        <v>-0.2072797617388415</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1500960070520433</v>
+        <v>0.1014402446640812</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.157938477960554</v>
+        <v>-0.02291373308627457</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.06965235351133925</v>
+        <v>-0.2189920882820773</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.05984355513689885</v>
+        <v>0.1823707078129936</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.2280483503220882</v>
+        <v>0.1701033452395062</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0125780175950362</v>
+        <v>0.1128476767196003</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.000182353790052766</v>
+        <v>0.0006025280952413857</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03325840607938998</v>
+        <v>0.1765947454003476</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.09781717639329661</v>
+        <v>-0.2227748352726378</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.08652717958817879</v>
+        <v>-0.06550444893682268</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1208459445999099</v>
+        <v>-0.1467565468229408</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2117543704039968</v>
+        <v>0.1775763698851325</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1914408757481791</v>
+        <v>-0.00286657295840801</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1276309546215755</v>
+        <v>-0.03141814798689905</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.07134820284485917</v>
+        <v>0.2274131992760764</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02833820333953185</v>
+        <v>0.1796661736939823</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1357579956393387</v>
+        <v>-0.005349234190169253</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.05400919354133963</v>
+        <v>0.02131500440540861</v>
       </c>
       <c r="BB5" t="n">
-        <v>-4.754780904362185e-05</v>
+        <v>0.009838291345582124</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.08780834092639642</v>
+        <v>-0.01733870753090586</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.2152607633185174</v>
+        <v>0.2157636950139063</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.1128577825065209</v>
+        <v>0.204298235208125</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1781925981349236</v>
+        <v>0.0218528902120784</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.007133814940756142</v>
+        <v>-0.08755996763074524</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.06302308924131295</v>
+        <v>-0.1340283227367075</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.08586726877354879</v>
+        <v>0.2288398724095404</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1605183638061863</v>
+        <v>-0.1705428323902632</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1614629512156524</v>
+        <v>-0.01832648539493776</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1803527055917744</v>
+        <v>-0.04192054151762774</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0002171019959048692</v>
+        <v>-0.1726978318301176</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.06644971017933085</v>
+        <v>-0.02465205984607244</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1555570536793202</v>
+        <v>-0.006658290199865058</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.06710496519661432</v>
+        <v>0.03082919536852657</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.1731933940718384</v>
+        <v>0.03637495795129182</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.04780569405894385</v>
+        <v>-0.03023935819337732</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.0003820815889812553</v>
+        <v>0.003432573728706867</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.1024999952288591</v>
+        <v>0.1653607321078202</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.006811937081418e-06</v>
+        <v>-8.460177034695355e-08</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.07721507504916982</v>
+        <v>0.06116819444897205</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.1096338340241146</v>
+        <v>0.08481673899401845</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.04022316053247779</v>
+        <v>-0.02669336737695108</v>
       </c>
       <c r="BY5" t="n">
-        <v>-5.435953015926552e-07</v>
+        <v>0.07319507027655243</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.064568534618789</v>
+        <v>0.005152792194290801</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.09902290813357427</v>
+        <v>-0.001449706725876142</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.04639028478039119</v>
+        <v>0.220160580547435</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.07873367196667985</v>
+        <v>-1.63986635771989e-05</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.02038281025920406</v>
+        <v>0.02735014064820005</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1164066284878348</v>
+        <v>0.1540274739165778</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.07780192768127885</v>
+        <v>0.2039830251480615</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.09836853865523959</v>
+        <v>-0.1470358611785951</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.07729259055639026</v>
+        <v>0.05367082042468821</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.2470540846112881</v>
+        <v>-0.1909879893211935</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.2137211383261528</v>
+        <v>-0.05712109037110094</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.1155606853729157</v>
+        <v>-0.0006598646131338151</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.007325869794536355</v>
+        <v>0.1661287470668931</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.1452462777803004</v>
+        <v>0.0004707786612570651</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01495298194168166</v>
+        <v>0.02887637654759291</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1445653774295418</v>
+        <v>-0.02818660517136364</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1795503447091702</v>
+        <v>-0.1624250165022351</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.03220707246559599</v>
+        <v>0.08211000103123972</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.03980339486329978</v>
+        <v>0.1104656093176145</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.1393606674901174</v>
+        <v>0.186141371730776</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.03252570830995822</v>
+        <v>-0.09683388730907333</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.2049331903449954</v>
+        <v>-0.08404813531291783</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.09403592871607062</v>
+        <v>-0.2035439882008503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.083232395558533e-06</v>
+        <v>2.600567049220982e-10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003726135874094787</v>
+        <v>0.2052303581199124</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1012373374957174</v>
+        <v>-1.396402670775923e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08116446675934984</v>
+        <v>0.1933739446165673</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08104446383532285</v>
+        <v>0.2415875613883619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1136939262234723</v>
+        <v>0.0741219389330405</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09500180480336272</v>
+        <v>-0.1063512694461539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06905374692395136</v>
+        <v>0.1063969873425392</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2355389394411763</v>
+        <v>-1.606559771548726e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1127839603035873</v>
+        <v>0.169801351083829</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1444568273777693</v>
+        <v>0.0396592483692836</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06089884654514809</v>
+        <v>-0.1750000590340081</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1807434379517648</v>
+        <v>0.02520012910277334</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09469443254278709</v>
+        <v>0.1889552110834526</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1715041089059231</v>
+        <v>-0.06842555317492825</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01223185701506187</v>
+        <v>0.2109275696907863</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2214393266039227</v>
+        <v>-0.1970100470975962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1751255522504534</v>
+        <v>5.18809850749548e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07206601648990564</v>
+        <v>0.1374735533067643</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08981224993023737</v>
+        <v>0.03226072911900514</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1295697230785582</v>
+        <v>0.0279755801947541</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1562747153679056</v>
+        <v>-0.04128474350942779</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0309492574007772</v>
+        <v>0.1106768050563092</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.09352556128015536</v>
+        <v>-0.1647389690469835</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1715639461645711</v>
+        <v>0.1366818713890604</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.07411964768600744</v>
+        <v>0.09848312447148405</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.06929128117268021</v>
+        <v>-0.2519132640287374</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0754131107150896</v>
+        <v>-2.175309228336798e-12</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.09083489855461685</v>
+        <v>-0.0780872626614058</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.05802148512988227</v>
+        <v>0.185087018765323</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1469974777286224</v>
+        <v>-0.01396575522167032</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.07698231398972397</v>
+        <v>0.01036402411504527</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.005333878083009687</v>
+        <v>0.07345360030003803</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.06332791235583002</v>
+        <v>0.1964397770946492</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.03180068687162419</v>
+        <v>-0.04518879857604378</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1166658756263881</v>
+        <v>0.02336346175054714</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1335812537110755</v>
+        <v>0.00841339661408705</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.1227853447088662</v>
+        <v>0.007118671161840619</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1278608160881288</v>
+        <v>0.07576472869398242</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07037948038573619</v>
+        <v>-0.05032615641202074</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.155783750154987</v>
+        <v>0.1880285409710878</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.1947473162735366</v>
+        <v>-0.004397927308157227</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.1061492584180864</v>
+        <v>0.2144790038582241</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1565884356876122</v>
+        <v>0.02223250375553137</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.523098109436974e-05</v>
+        <v>0.1738755188880503</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1782031503035171</v>
+        <v>-0.1096488003139079</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.06523693977929237</v>
+        <v>0.1301212784596683</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.1825557141575389</v>
+        <v>-0.01854279967254182</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.1069108702395587</v>
+        <v>0.1955912895394289</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0005588663834089506</v>
+        <v>0.001193350995277551</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.08602593608990138</v>
+        <v>-0.1090277126627539</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.07194542332221648</v>
+        <v>-9.26249914145034e-08</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.01130563537028546</v>
+        <v>-0.1225531329532932</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00136910788676606</v>
+        <v>-0.1210830136140441</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.004728227382782859</v>
+        <v>-0.003992149179809911</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1502948565811508</v>
+        <v>0.2057318172892052</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.02944261425127895</v>
+        <v>-0.03952253789878984</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.2061608471366515</v>
+        <v>0.0517978802769537</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002552218103732567</v>
+        <v>0.1398990696187461</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.04307416352609791</v>
+        <v>-0.2187034194620273</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.2193568161336752</v>
+        <v>-0.2165913851977678</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1437787278133175</v>
+        <v>0.1230860608803125</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.06426920661673337</v>
+        <v>-0.001874959859419773</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.2079165703023679</v>
+        <v>-0.1104338768923869</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.005540458360530087</v>
+        <v>0.08826556266649403</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01248017899971487</v>
+        <v>0.1928397551976297</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.05001159739864972</v>
+        <v>0.1525546586463894</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2151409318829907</v>
+        <v>-0.2016757023490214</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.2253199520918001</v>
+        <v>0.1645461861996572</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.05645288720348662</v>
+        <v>0.1362527567830195</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.04980541180540483</v>
+        <v>-0.01556069141030343</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.1788491711914739</v>
+        <v>-0.1678083749121017</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.03752339730214151</v>
+        <v>-0.02089922019990999</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.208198552689626</v>
+        <v>-0.1492137012464567</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.1528527223370262</v>
+        <v>-0.06865549950512505</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.1888337267039228</v>
+        <v>-0.02982891377956441</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.02903418293854184</v>
+        <v>0.02587744582372708</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.04694458611708065</v>
+        <v>0.0380746129530735</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1201209770084628</v>
+        <v>-2.746031663341799e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.2498522202680189</v>
+        <v>-0.05199527342954666</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0551985677401248</v>
+        <v>-9.167337135453376e-06</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.04542740462025376</v>
+        <v>0.0005871973295102967</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1219982921072075</v>
+        <v>-0.05649109436289207</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.1508360043708651</v>
+        <v>-0.04192758225774266</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.004908363581192727</v>
+        <v>0.005346614549505597</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.1889477526153465</v>
+        <v>0.04835252574793277</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1243441793306946</v>
+        <v>0.2375538549004765</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01558307266323572</v>
+        <v>-0.1841510068727287</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.2027280556836646</v>
+        <v>2.419892098367013e-08</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.06844957642998963</v>
+        <v>-0.2007600004385621</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.07164696180070231</v>
+        <v>-0.0001141635723209361</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01547161990401478</v>
+        <v>-0.01348908860184011</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.008881739993477836</v>
+        <v>4.64151871532067e-11</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1789017784173987</v>
+        <v>0.209154272759337</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.003390567312165211</v>
+        <v>-0.1942231899459366</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.09272302714070313</v>
+        <v>0.1716363899228047</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.216847998996759</v>
+        <v>0.2067870773221791</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.1607224486929311</v>
+        <v>0.2079734617498984</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.09155111928800944</v>
+        <v>-0.07457197105938138</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.2280713360748676</v>
+        <v>-0.1897950781472561</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.05478297445852773</v>
+        <v>-0.01322113121660922</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1310178907970518</v>
+        <v>0.007204876965418604</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1523023730904699</v>
+        <v>0.02161304380939646</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06101006887030468</v>
+        <v>0.1709036752211812</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06691284399485457</v>
+        <v>-0.03425133959203424</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262552802330646</v>
+        <v>-0.08071468245261784</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03948177831009599</v>
+        <v>0.1417407264974103</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07429119264168968</v>
+        <v>-0.06412098926964105</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02772829702442821</v>
+        <v>-0.02941496147474568</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1216997050251443</v>
+        <v>0.125197659495331</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1256763365193062</v>
+        <v>0.1089861785472726</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1592132215067312</v>
+        <v>0.1322653811966227</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03538473220111313</v>
+        <v>0.2159115740831835</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.003272349318951064</v>
+        <v>-0.0538614962691239</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0282147685036972</v>
+        <v>0.05321977350811427</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.002969029926184133</v>
+        <v>0.1884530826575153</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0001249200405592756</v>
+        <v>0.1836931483498638</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.131416758545237</v>
+        <v>-0.008458820639551648</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06891131969194515</v>
+        <v>-0.1696501828938908</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06042589438162901</v>
+        <v>0.2264059664054531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2048746699238127</v>
+        <v>0.02783877998134057</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1249602196310585</v>
+        <v>-0.1076290762587637</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08520555505436574</v>
+        <v>0.02935603444596951</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08556769191178393</v>
+        <v>-0.2250423528140394</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1537476233762944</v>
+        <v>0.06225802045241664</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.05425960105880261</v>
+        <v>0.1622499404663895</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1944887732788196</v>
+        <v>-0.14956020474416</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.09870823458517106</v>
+        <v>-6.43403161951984e-08</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1614329389725142</v>
+        <v>-0.1070108889172624</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1925182057039694</v>
+        <v>0.119806393330157</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.06195002414880174</v>
+        <v>0.1990791237835409</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02811859725371396</v>
+        <v>-0.06151059717270461</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.07573382325163709</v>
+        <v>-0.1296977023735133</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1861992673963438</v>
+        <v>0.07358046369174892</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.000639740509297746</v>
+        <v>0.1039982302832573</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.233719693195671</v>
+        <v>0.101339052867552</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1636658334453389</v>
+        <v>-2.380907227565106e-09</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.1113090856155938</v>
+        <v>0.207280625176265</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.1822511232625132</v>
+        <v>-0.01938180328333998</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.04257172053150308</v>
+        <v>-0.02848300694968602</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.09196339203971239</v>
+        <v>-0.1725849605924443</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.09195091889992842</v>
+        <v>-1.356735933665272e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.06540860318379212</v>
+        <v>0.1365282187559018</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1120800229181921</v>
+        <v>0.02888814197811218</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.002550404609652322</v>
+        <v>-0.1396283289023486</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.02890227525094152</v>
+        <v>-0.2100550403182033</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1102986572951546</v>
+        <v>0.05203712549073831</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.1514979797992649</v>
+        <v>-0.03022772399332735</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.01906763607138567</v>
+        <v>-0.07659003197188048</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.01759503451273395</v>
+        <v>0.08090183345170543</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02664538017907919</v>
+        <v>-0.05789286882308689</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.2155322511948797</v>
+        <v>0.01775200958093217</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.07413659370078662</v>
+        <v>-0.04884735863737485</v>
       </c>
       <c r="BB7" t="n">
-        <v>-1.883230118756717e-06</v>
+        <v>-0.08898977443138346</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1031597930374396</v>
+        <v>0.007195942561445562</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1494189694069982</v>
+        <v>-0.009456989609148257</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.07584106648884309</v>
+        <v>0.01109908637324697</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.07618062513629703</v>
+        <v>-0.0854925809507457</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.06101123776099027</v>
+        <v>-0.1187882643834521</v>
       </c>
       <c r="BH7" t="n">
-        <v>-1.836394511035486e-05</v>
+        <v>-0.11797784055276</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1760006339144496</v>
+        <v>0.1508731219081557</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.04119411870709921</v>
+        <v>-0.2173394579416776</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0577415947656349</v>
+        <v>3.54882204045841e-10</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.2409872639878545</v>
+        <v>0.1689920816479129</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0004158480937211126</v>
+        <v>0.08468569392305635</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003409716106101891</v>
+        <v>0.176734135202913</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1014762100971933</v>
+        <v>-0.1912983752493506</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.1619282252592114</v>
+        <v>0.007187435669410858</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.1382189949744771</v>
+        <v>-0.1581656241805064</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.2329948819014771</v>
+        <v>0.08475334594716274</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.05268266231050971</v>
+        <v>0.02694222704250641</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.009870169227449526</v>
+        <v>-0.01336799473163795</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.00773855908537012</v>
+        <v>-0.0001179717292665086</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.2386686510776715</v>
+        <v>0.04190019032743325</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01917282458223347</v>
+        <v>0.001930289849995186</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2052619145102839</v>
+        <v>0.2300529030063317</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.609958873394736e-05</v>
+        <v>-0.02785092937197146</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.1699511926797071</v>
+        <v>-0.2046425758998806</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.1600114545068682</v>
+        <v>2.19387428494399e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1509458373987169</v>
+        <v>0.01690989745834221</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.02825640620300508</v>
+        <v>8.119218184054391e-11</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.03937042492836884</v>
+        <v>-0.1259974834017812</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.2629111708054223</v>
+        <v>0.1084048169960757</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.05625190547277542</v>
+        <v>0.2351379761079625</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.08234041124863196</v>
+        <v>-0.2483474211766903</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.104871060819254</v>
+        <v>-0.2550242188234316</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.06422646527393593</v>
+        <v>0.05691046044992272</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0114210654774826</v>
+        <v>0.2197644976557648</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.01339478352208875</v>
+        <v>2.815480671140475e-08</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.005872743622392946</v>
+        <v>-0.004070531357625863</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.04187875061581107</v>
+        <v>1.000436770577907e-09</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01760696005541755</v>
+        <v>0.04004392102776825</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.09774067895728088</v>
+        <v>-0.01661248075802164</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.100090023957789</v>
+        <v>0.03793302185608882</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.008943600098163331</v>
+        <v>-0.1201024178963852</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.03382366129120803</v>
+        <v>0.03849125407448054</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.02921413145112007</v>
+        <v>-0.1086664251782602</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.09951438991712817</v>
+        <v>0.1946967587761199</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.02978572843121394</v>
+        <v>0.09805776469207073</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.1469799753508997</v>
+        <v>0.1941674702023835</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
@@ -732,1814 +732,1814 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.0100777373946481</v>
+        <v>-0.0650095127821495</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0002611490568513757</v>
+        <v>0.1630669102941881</v>
       </c>
       <c r="C2" t="n">
-        <v>3.588467043203067e-10</v>
+        <v>-1.539698749195595e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0845163267885278</v>
+        <v>0.1545747142539464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04409236589353237</v>
+        <v>-0.1006837899595165</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01241980387588445</v>
+        <v>-0.2216125158764755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1278599899058752</v>
+        <v>0.1942614750504184</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1079323142862748</v>
+        <v>0.07332365587173732</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.258303372821985e-10</v>
+        <v>-0.1020098032370384</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1918880320889485</v>
+        <v>-0.1604086145594978</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1483640259096808</v>
+        <v>-0.0338153867929662</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1013467984451662</v>
+        <v>-0.1601980609737831</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2545420056317152</v>
+        <v>-0.187609044175817</v>
       </c>
       <c r="N2" t="n">
-        <v>0.180360172011658</v>
+        <v>-0.1158729266751317</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1285582344944099</v>
+        <v>-0.09853437299218173</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2705035498389899</v>
+        <v>0.1251367201650667</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.02108352715813281</v>
+        <v>0.1437366475372206</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001123488091381433</v>
+        <v>-0.06859068191156027</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1064882104407642</v>
+        <v>-0.2072944402125654</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0442450459374919</v>
+        <v>0.1234136430654343</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.01606931579525504</v>
+        <v>-0.05542731712833387</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1381212043437244</v>
+        <v>0.06414343640691283</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.02977139623942329</v>
+        <v>0.03386767606924318</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02169283238441352</v>
+        <v>0.1009779737715781</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1927955048552167</v>
+        <v>0.1107683938210098</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01976931776211168</v>
+        <v>0.05794781308096283</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.07609981839734863</v>
+        <v>0.02587080641743696</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.753016565849269e-06</v>
+        <v>-0.08902312554303737</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05072327981303794</v>
+        <v>-0.2206679278827498</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2023042593651587</v>
+        <v>-0.001555605675969562</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.205324892762822</v>
+        <v>0.08015413413380615</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.182744966255898</v>
+        <v>0.0299073711234599</v>
       </c>
       <c r="AG2" t="n">
-        <v>-5.483838776901589e-07</v>
+        <v>-0.05451796887972863</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.2098218207357924</v>
+        <v>0.02423449925659326</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.2368706144278402</v>
+        <v>0.1585720188772259</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1755351823377795</v>
+        <v>0.006767319295815383</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.502513498578456e-05</v>
+        <v>0.1901071114161105</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.08405314373093732</v>
+        <v>0.1392075259852637</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.09276499410618992</v>
+        <v>0.09408774318568515</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.000499674985468305</v>
+        <v>-0.04602421455574521</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1176434549958445</v>
+        <v>-0.1249048656325981</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.03335381676007687</v>
+        <v>0.1202960208184117</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.04712343965211781</v>
+        <v>-0.1148579706807173</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.0008939854611719594</v>
+        <v>-0.1037313284726938</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.1829533176177319</v>
+        <v>0.0623090637852768</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02903855565113455</v>
+        <v>0.2053787799573603</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1406009945277586</v>
+        <v>-0.1083595594679824</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.224663393263067e-09</v>
+        <v>-0.1097207125509886</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.005939369686492252</v>
+        <v>0.09844624199187207</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.187708311967764</v>
+        <v>-0.0003498180729842019</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.2285666972898632</v>
+        <v>-0.03858051325145134</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01234355513533185</v>
+        <v>0.04895600184754943</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1674111496147841</v>
+        <v>0.09330600920802147</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.005711689948774746</v>
+        <v>-0.01456908884706475</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.006455410696953328</v>
+        <v>0.08981961007436687</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.06231850684046125</v>
+        <v>-0.005122529095361707</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.2037015423404008</v>
+        <v>-0.04818791057702902</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.1310029442328044</v>
+        <v>-0.01789229978575759</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.09131623177981425</v>
+        <v>0.1087888452031312</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1995267976559436</v>
+        <v>-0.2150954960806389</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.07176185228958198</v>
+        <v>0.1774705471959754</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1235408020742824</v>
+        <v>-0.1160187348825773</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.005018741545351506</v>
+        <v>0.0663332255748095</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.06943078684244844</v>
+        <v>0.02907699843372174</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.005627566805453265</v>
+        <v>-0.128249011168787</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1669338144158722</v>
+        <v>0.04872435406360103</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.07715965750681182</v>
+        <v>0.07187989965935022</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.2029959676356316</v>
+        <v>0.001282401638263761</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.203875810633749</v>
+        <v>0.1217183481143771</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.1964863765168867</v>
+        <v>-0.06621472705762271</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.003425925395437803</v>
+        <v>0.1296161261765075</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.005004944306798741</v>
+        <v>0.06350896041663311</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.02214484593133721</v>
+        <v>0.1731801956550992</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1517685784034685</v>
+        <v>-0.01335922099316914</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.2211334802992808</v>
+        <v>-0.06654285324367977</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.04510580138335059</v>
+        <v>-0.1517768250292516</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1391405099039476</v>
+        <v>-0.05273614377190336</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.1875193452647843</v>
+        <v>-0.1308186566264896</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.02967669409524809</v>
+        <v>0.0002086932397401231</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.230799518790217</v>
+        <v>-0.03995720776582944</v>
       </c>
       <c r="CC2" t="n">
-        <v>-2.644447479230682e-08</v>
+        <v>0.06027620788899413</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0002362615276252102</v>
+        <v>-0.151717610486308</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1586892409307296</v>
+        <v>0.1571622933052727</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.08103173382136092</v>
+        <v>-0.0642817399558217</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.2086272446373512</v>
+        <v>0.07333535703652315</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.07784262046928017</v>
+        <v>-0.06632901467990274</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.1320578529034222</v>
+        <v>-0.2466438167655948</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0.1619176139700363</v>
+        <v>0.1567966541465195</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.071902672675909e-10</v>
+        <v>0.09595109816794033</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.186982152430455</v>
+        <v>0.1102820435413953</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.006012252468416446</v>
+        <v>0.001010525050066213</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.2052141815452515</v>
+        <v>-0.008455541147542227</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.0007288607384794353</v>
+        <v>-0.09505791885038307</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.1823305856055239</v>
+        <v>0.04385982011392833</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.1355872468447399</v>
+        <v>0.104942524816108</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.1756401051607913</v>
+        <v>0.2220937545807433</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.06082698203071486</v>
+        <v>0.03411146037730215</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.1467181359187702</v>
+        <v>-0.000195305988395338</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.1049744861794819</v>
+        <v>0.1742397089348392</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.01023537723573164</v>
+        <v>0.03274528335049792</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.0243760660932431</v>
+        <v>-0.03119520546878109</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.1926660158130944</v>
+        <v>0.05453828941045789</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.004138307677941447</v>
+        <v>-0.06375999550855412</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1178315001274852</v>
+        <v>0.2317561190642877</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03277199406260532</v>
+        <v>-0.2375617017432221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1382079547773834</v>
+        <v>0.1086257218248655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.131269028892073</v>
+        <v>-0.2376190986556549</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1570996379984181</v>
+        <v>-0.2352161927611187</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.273781225431475e-05</v>
+        <v>-0.2281857475459848</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2170129864442782</v>
+        <v>0.1975115056302851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03641661029840765</v>
+        <v>0.2392577970659195</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05005544006271122</v>
+        <v>0.1934402739207028</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.006198663467795782</v>
+        <v>0.1813287629922346</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05630311146660292</v>
+        <v>0.07272068272962744</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06619394411201843</v>
+        <v>-0.03926685273979127</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1379987099203453</v>
+        <v>-0.1523525462168346</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002303195377910126</v>
+        <v>-0.2403290508438006</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0003838373897727128</v>
+        <v>-0.08690488436777306</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1585752543723175</v>
+        <v>0.1196122778107567</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004117678780489795</v>
+        <v>-0.01179221896514384</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0008254609695767673</v>
+        <v>0.0001620666541513278</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1310455407498445</v>
+        <v>-0.09959936660607181</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08205727289286767</v>
+        <v>0.05902080386386828</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.224003604476614</v>
+        <v>-0.2187102848360645</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.09799183355951938</v>
+        <v>0.2233493037555076</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01767971033843684</v>
+        <v>2.06235092228304e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2198006408809138</v>
+        <v>-0.2059827396833024</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.02111594699963395</v>
+        <v>-0.1385083588148613</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1178210712282283</v>
+        <v>0.08473528926712558</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.08974189542576794</v>
+        <v>0.008499216908993726</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.06832818955964509</v>
+        <v>0.1307988280390748</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2354655639675341</v>
+        <v>-0.02736812711998397</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.006140068442158103</v>
+        <v>-0.04329355812861513</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09323340383782544</v>
+        <v>-0.1427439602662426</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2160845761034486</v>
+        <v>-0.1057761678307341</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07847808004637785</v>
+        <v>-0.01319147622269065</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.01018471894234884</v>
+        <v>0.1262573648435981</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2205133179767585</v>
+        <v>-0.1383588825744323</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.05781704335718713</v>
+        <v>0.1397518764108172</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.01240569741292299</v>
+        <v>-0.1086146742579395</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.05568328990896248</v>
+        <v>0.05214649177087152</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.03273562768971706</v>
+        <v>0.08302392115339642</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2404505869372031</v>
+        <v>-0.162501031307067</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.02149050845031608</v>
+        <v>0.001590560619028915</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1831031751092731</v>
+        <v>-0.2238517576270987</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.217881528863039</v>
+        <v>0.06603605088309963</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0191459924811852</v>
+        <v>0.1121311388762331</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.01438829635301897</v>
+        <v>-0.153706689623947</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08173232770322314</v>
+        <v>-0.07083839372854907</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.213189742082947</v>
+        <v>-0.1005591694425817</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.07417451564038897</v>
+        <v>0.1940395884827074</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.01675396843516716</v>
+        <v>-0.1543779664168168</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.198798814416085</v>
+        <v>0.08627624847153828</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.2036470617562921</v>
+        <v>-0.05065279388868678</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01742431312698485</v>
+        <v>0.2495761447314426</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.137379661288222</v>
+        <v>-0.08503900522103415</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.2000860465509342</v>
+        <v>-0.06419444574224105</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.06407103092483099</v>
+        <v>-0.02364752468964018</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.09329429868710225</v>
+        <v>0.1194635548354593</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1676265673807719</v>
+        <v>-0.1859881249896693</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0620637239738225</v>
+        <v>0.211792904795831</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.07354716643392284</v>
+        <v>-0.181831760702864</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.008893073723788666</v>
+        <v>-0.0619007442467441</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1138137960371383</v>
+        <v>0.2059874369994993</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0132472887023793</v>
+        <v>0.1567162287052302</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0281906460874927</v>
+        <v>-0.01768233964885746</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.03511482127588324</v>
+        <v>0.08606715501448396</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1224271736597198</v>
+        <v>-0.08989315594141291</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.02242371675886514</v>
+        <v>0.06463601447548735</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2211304990320193</v>
+        <v>0.1292094672946035</v>
       </c>
       <c r="BS3" t="n">
-        <v>-3.970995835467419e-09</v>
+        <v>-0.09003198300276526</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.191635380789938</v>
+        <v>-0.05250491933874606</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.00417697579844268</v>
+        <v>0.1797790699825099</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.09783940930156271</v>
+        <v>-0.1066216285385268</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.1839179250458111</v>
+        <v>-0.08528597869940471</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.09931031877151396</v>
+        <v>0.04791848899268621</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2214255248817569</v>
+        <v>0.07478960973426867</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.03051974118994675</v>
+        <v>0.08662428021241814</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.003160941291248043</v>
+        <v>-0.01401113212213608</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.07117773932538626</v>
+        <v>-0.06379124777058717</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.006627881877736519</v>
+        <v>-0.03093516170377981</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.01171027094525793</v>
+        <v>0.2132087912911065</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1596261568063791</v>
+        <v>-0.07712532488449962</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.1240059328348251</v>
+        <v>0.1770496942314913</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.173138504745595</v>
+        <v>0.1505873629698374</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.04609793955728853</v>
+        <v>-0.08587463899088228</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.1039120596991157</v>
+        <v>0.2299452914296656</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1880316759957957</v>
+        <v>0.1699168080028989</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0007426996758293498</v>
+        <v>-0.03252890562652494</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01650102593414619</v>
+        <v>0.1340053448465273</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.001468888222168598</v>
+        <v>-0.002884511461070465</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1437304709707952</v>
+        <v>-2.662261469589017e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0001209263226468192</v>
+        <v>-0.2270666051529409</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1507188518613406</v>
+        <v>0.002581353052225721</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1591773742647429</v>
+        <v>0.1175671119787897</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.2030355359256676</v>
+        <v>-0.0742350572167562</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.02109729942492018</v>
+        <v>-0.1704858897082024</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.09425493857725191</v>
+        <v>-4.041800679597918e-05</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1064736358472799</v>
+        <v>0.1495729386857374</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.2235396019304792</v>
+        <v>-0.1444808653544986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.02757969927237838</v>
+        <v>0.09501781419195775</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.2314037231233215</v>
+        <v>0.1138904471476487</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0003967618830383748</v>
+        <v>-2.40138304418787e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1686493691129793</v>
+        <v>0.001249723363203378</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04727346007223469</v>
+        <v>0.05642589678164112</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09615708195230668</v>
+        <v>-0.1121806629252453</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07564574081704679</v>
+        <v>-0.01458226951781372</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08928189646370627</v>
+        <v>0.1831143513143489</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0006218762106009092</v>
+        <v>0.1656356817848606</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1737543400003882</v>
+        <v>0.1960732748996663</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1758429285981551</v>
+        <v>0.1281980483050676</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.009750779013789302</v>
+        <v>-0.08907105877230269</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0694345751720658</v>
+        <v>0.1552538348314348</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01516343154911078</v>
+        <v>-0.2453306432244059</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2254473535351857</v>
+        <v>-0.0338417236432365</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2431554541547989</v>
+        <v>0.02418669660465718</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1170200491359288</v>
+        <v>0.134545776146368</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.004215126348508353</v>
+        <v>-0.05037031548662523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2239392930785137</v>
+        <v>0.06565947728528181</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07687212453421768</v>
+        <v>0.1055930060112348</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1074119301659689</v>
+        <v>-0.1016962785025836</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1956272489977672</v>
+        <v>-0.000807821901244148</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.008954241917425004</v>
+        <v>0.03098766968835787</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1049710200784925</v>
+        <v>0.1454580123612128</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.04258380992542456</v>
+        <v>0.1411599763108849</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1545576006969112</v>
+        <v>-0.02670350112988821</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2156299218754159</v>
+        <v>-0.04408077671298922</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.01841173564884781</v>
+        <v>0.08671681642743607</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1082999753200555</v>
+        <v>-0.2198707688373748</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2315369074497849</v>
+        <v>-0.09610872002527918</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2249334700735044</v>
+        <v>0.1207615152048892</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1275356950954361</v>
+        <v>-0.02477469081485355</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.1665157610876005</v>
+        <v>0.13791278027459</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03199302104644162</v>
+        <v>0.06085036366942632</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1819802494206454</v>
+        <v>-0.01525742687676825</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.2302070010680962</v>
+        <v>-0.02941684119181699</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.01441589513667496</v>
+        <v>0.1329479688955668</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1775099312366429</v>
+        <v>0.01064237249885369</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.08812902941066621</v>
+        <v>-0.1609600547367056</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.06236518848401036</v>
+        <v>-0.1425025542281628</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.1528675008972045</v>
+        <v>-0.04152748100418093</v>
       </c>
       <c r="AP4" t="n">
-        <v>-4.254452614534407e-05</v>
+        <v>0.1723889717889768</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001584810723238469</v>
+        <v>0.2220403758288574</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.07621445099512332</v>
+        <v>-0.07889144179355405</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.212605856277305</v>
+        <v>0.155060923112196</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.157449229852237</v>
+        <v>-0.1019864319421312</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1607621761821132</v>
+        <v>-0.0713400938227222</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.00151938292313805</v>
+        <v>0.2302107917418741</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.1829449584513241</v>
+        <v>-0.05902269070646989</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.009691674394021191</v>
+        <v>-0.09616476712993068</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1580107366750233</v>
+        <v>0.1720417039406072</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.001676901445505775</v>
+        <v>0.01068530382292025</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1979319692608522</v>
+        <v>-0.09293059570446784</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03973481995684146</v>
+        <v>3.649635677079004e-06</v>
       </c>
       <c r="BC4" t="n">
-        <v>-3.486004140108568e-11</v>
+        <v>-0.07686417762330013</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.1776565459330303</v>
+        <v>-5.189794820853525e-07</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1246848176963441</v>
+        <v>-2.286672902397692e-07</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0005029873813741576</v>
+        <v>-0.01536147967683698</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1245754727290255</v>
+        <v>-0.1064190777552721</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.0858708441214137</v>
+        <v>0.2290708626700839</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.2044242582529439</v>
+        <v>0.0543760679901078</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.05900976814149644</v>
+        <v>0.03158648015893108</v>
       </c>
       <c r="BK4" t="n">
-        <v>-4.984724237814561e-09</v>
+        <v>0.06955094663856611</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.06452650647725171</v>
+        <v>-0.07486062688706403</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.09274988316627443</v>
+        <v>-0.1848006468326213</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.2041746731738801</v>
+        <v>-8.996177734170057e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1129208202843112</v>
+        <v>-0.1949937628856506</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.03262096700337323</v>
+        <v>-0.02862200300165913</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.2284979804051837</v>
+        <v>-0.03031676093053352</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1270545345862752</v>
+        <v>0.1283233600089602</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.01385191208318505</v>
+        <v>0.1673309386110468</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.05653720553214762</v>
+        <v>-0.04531013323211822</v>
       </c>
       <c r="BU4" t="n">
-        <v>-1.96799662007476e-11</v>
+        <v>-0.1600674108037209</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.09042547261640183</v>
+        <v>-0.009339728953641416</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02681703273962846</v>
+        <v>-0.02621130832453275</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.1455853688519574</v>
+        <v>-0.184526791546963</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.2089025384215928</v>
+        <v>-0.2274657856537918</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1410379088925134</v>
+        <v>0.1916344356910789</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0.0002293586367742409</v>
+        <v>-0.03535742148159968</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.08617720928259331</v>
+        <v>-0.001893296899297594</v>
       </c>
       <c r="CC4" t="n">
-        <v>-3.820219207923317e-08</v>
+        <v>-0.04283117496483914</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.1617160169007852</v>
+        <v>-0.1991402573909706</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.01780729594532531</v>
+        <v>-0.07337572331301979</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1103575952984874</v>
+        <v>-0.2066986871481866</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.04238397006647134</v>
+        <v>-0.1115037713378876</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.2016148250438523</v>
+        <v>-0.200345964677312</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005971685427632545</v>
+        <v>-0.08127228664792099</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1157110796606582</v>
+        <v>0.1098106679131062</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.898156916354277e-10</v>
+        <v>-0.03519191496940405</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.07312428514040065</v>
+        <v>-0.177129336983915</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.01714968691242642</v>
+        <v>-8.068840258492895e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1386371627549529</v>
+        <v>-0.004524654024415712</v>
       </c>
       <c r="CO4" t="n">
-        <v>-2.794317414876946e-06</v>
+        <v>0.07652786645402841</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.06543410186112596</v>
+        <v>0.06577279864043899</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1014767386848307</v>
+        <v>-0.1662030042380093</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.213143755898683</v>
+        <v>0.1310120313495333</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1259730430504759</v>
+        <v>0.1664178521305204</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0.1104365416032521</v>
+        <v>-0.03096324335603241</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.1712019086087697</v>
+        <v>0.2098387359458961</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2361331459881215</v>
+        <v>0.125034879772089</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.02157669213709057</v>
+        <v>0.2261320700717534</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04327525726169842</v>
+        <v>-0.1815073024891113</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000267555634944832</v>
+        <v>0.0004442477955449186</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1494427348111508</v>
+        <v>0.2269914066815974</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07669461518150904</v>
+        <v>-0.07852746653815038</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1847145975477987</v>
+        <v>-0.2198826610281876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1643592198206955</v>
+        <v>0.2185920831726928</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08266000842821067</v>
+        <v>0.002915921977387343</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.208141857702821e-05</v>
+        <v>-0.2152204016016696</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1594152018221891</v>
+        <v>0.01219363171577638</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.05028692924552683</v>
+        <v>-0.158074753246879</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1479350008703972</v>
+        <v>-0.04377570536062304</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.116085537767525</v>
+        <v>0.2045797397085301</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2412275939538686</v>
+        <v>0.004202348279729898</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.09671769209456971</v>
+        <v>0.1339898924352934</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1548872557368859</v>
+        <v>-0.2059809581356347</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1055063570489502</v>
+        <v>0.01936323680428024</v>
       </c>
       <c r="R5" t="n">
-        <v>3.58364544492198e-05</v>
+        <v>0.03488815058204871</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1370837420917866</v>
+        <v>-0.005264671911670426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1346104748888121</v>
+        <v>-0.2310714302475455</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0236217249271591</v>
+        <v>-0.07633292904883759</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1292572740387446</v>
+        <v>0.07935253116665533</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1245641005714984</v>
+        <v>-0.1970253332892179</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1904343120016914</v>
+        <v>-0.1814165284775302</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.07473418397563109</v>
+        <v>0.1755382499551779</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04538141671594647</v>
+        <v>0.00293425384594352</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.02417247410404122</v>
+        <v>0.06477625919928179</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0003446659977204049</v>
+        <v>-0.2004534571780427</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1936842563719671</v>
+        <v>0.06713542012748036</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1084237001459652</v>
+        <v>-0.03332726500276095</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2307752836427098</v>
+        <v>0.1707750460211278</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.2341908941149027</v>
+        <v>-0.0004036293135947124</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1060763200543335</v>
+        <v>0.01579452944261377</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.08448256720194276</v>
+        <v>0.2340565095940542</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.2072797617388415</v>
+        <v>0.1799144737718006</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1014402446640812</v>
+        <v>-0.02407868291285258</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02291373308627457</v>
+        <v>-0.1852381992665146</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.2189920882820773</v>
+        <v>0.1633449273608423</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1823707078129936</v>
+        <v>0.1921525759309105</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.1701033452395062</v>
+        <v>0.0143370526500892</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1128476767196003</v>
+        <v>0.01582884048439632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0006025280952413857</v>
+        <v>0.07070892136993191</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.1765947454003476</v>
+        <v>-0.004103463837791639</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.2227748352726378</v>
+        <v>-0.04582414974018842</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.06550444893682268</v>
+        <v>-0.1526070997585837</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.1467565468229408</v>
+        <v>-0.01602266461008885</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1775763698851325</v>
+        <v>0.1284073823816484</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.00286657295840801</v>
+        <v>-0.1388836218152615</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.03141814798689905</v>
+        <v>0.02293654136790474</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2274131992760764</v>
+        <v>-0.001004687076766759</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1796661736939823</v>
+        <v>0.09929951764222363</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.005349234190169253</v>
+        <v>-0.1406670081777398</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.02131500440540861</v>
+        <v>-0.1311066581136189</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.009838291345582124</v>
+        <v>-0.05854293634520058</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.01733870753090586</v>
+        <v>-0.1099506933363389</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.2157636950139063</v>
+        <v>-0.06755280140061791</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.204298235208125</v>
+        <v>-0.05787324500867525</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0218528902120784</v>
+        <v>0.003667474534957107</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08755996763074524</v>
+        <v>-0.1238345836543889</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.1340283227367075</v>
+        <v>-0.1417247094495514</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.2288398724095404</v>
+        <v>0.161895446738979</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.1705428323902632</v>
+        <v>0.06947601207145619</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01832648539493776</v>
+        <v>-0.02479006923027341</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.04192054151762774</v>
+        <v>-0.002190555323842778</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.1726978318301176</v>
+        <v>-0.06333946241566218</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02465205984607244</v>
+        <v>-0.04777842196488042</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006658290199865058</v>
+        <v>0.004045446943631141</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.03082919536852657</v>
+        <v>-0.1034134689789705</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.03637495795129182</v>
+        <v>-0.2124980917595456</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.03023935819337732</v>
+        <v>-0.1957892062458037</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.003432573728706867</v>
+        <v>-0.1964647515366472</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1653607321078202</v>
+        <v>0.07943701362415663</v>
       </c>
       <c r="BU5" t="n">
-        <v>-8.460177034695355e-08</v>
+        <v>-0.08340041952272123</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.06116819444897205</v>
+        <v>8.180580873570866e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.08481673899401845</v>
+        <v>-0.0009629820730711208</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.02669336737695108</v>
+        <v>0.2312768102039145</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07319507027655243</v>
+        <v>0.2141203618549144</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.005152792194290801</v>
+        <v>0.2023602467586924</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.001449706725876142</v>
+        <v>0.008260605605144921</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.220160580547435</v>
+        <v>-0.001024579744018268</v>
       </c>
       <c r="CC5" t="n">
-        <v>-1.63986635771989e-05</v>
+        <v>-0.04985530286270144</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.02735014064820005</v>
+        <v>0.1948657764247243</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1540274739165778</v>
+        <v>0.2313364196959402</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.2039830251480615</v>
+        <v>0.222271309190945</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.1470358611785951</v>
+        <v>0.2016544748197904</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.05367082042468821</v>
+        <v>0.02458534960029615</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.1909879893211935</v>
+        <v>-0.05866572572225832</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.05712109037110094</v>
+        <v>0.1173818849418641</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0006598646131338151</v>
+        <v>-0.00689269340349811</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1661287470668931</v>
+        <v>-0.1941912545643686</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0004707786612570651</v>
+        <v>-0.04622180821213522</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02887637654759291</v>
+        <v>-0.1008898870098774</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.02818660517136364</v>
+        <v>-0.1375533193785859</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1624250165022351</v>
+        <v>-0.1194613415929378</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.08211000103123972</v>
+        <v>0.1546522523071668</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1104656093176145</v>
+        <v>-0.05274272625808182</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.186141371730776</v>
+        <v>0.1580214248856845</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.09683388730907333</v>
+        <v>0.0002639336045600893</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.08404813531291783</v>
+        <v>0.1022254003487066</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.2035439882008503</v>
+        <v>-0.2279260508147205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.600567049220982e-10</v>
+        <v>-0.01321694901044968</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2052303581199124</v>
+        <v>0.1291495474963885</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.396402670775923e-09</v>
+        <v>-0.009338843998996104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1933739446165673</v>
+        <v>0.09758549982235988</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2415875613883619</v>
+        <v>-0.1899709712988017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0741219389330405</v>
+        <v>0.2076539621767808</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1063512694461539</v>
+        <v>-0.162835076570134</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1063969873425392</v>
+        <v>-0.01908526804444344</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.606559771548726e-05</v>
+        <v>0.05659184863102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.169801351083829</v>
+        <v>0.1153790556332604</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0396592483692836</v>
+        <v>0.1887235121419928</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1750000590340081</v>
+        <v>-0.1577904557779105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02520012910277334</v>
+        <v>-0.1232197238322278</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1889552110834526</v>
+        <v>0.1517497353192374</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06842555317492825</v>
+        <v>0.1571272649391423</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2109275696907863</v>
+        <v>0.04163643480113024</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1970100470975962</v>
+        <v>-0.1336793374258129</v>
       </c>
       <c r="R6" t="n">
-        <v>5.18809850749548e-06</v>
+        <v>-0.0008471337609780882</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1374735533067643</v>
+        <v>0.2020341387364801</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03226072911900514</v>
+        <v>-0.164187383858232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0279755801947541</v>
+        <v>6.07746163914118e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.04128474350942779</v>
+        <v>-0.07982595211151809</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1106768050563092</v>
+        <v>0.15215159846458</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1647389690469835</v>
+        <v>-0.08460809824649181</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1366818713890604</v>
+        <v>0.02198297863485373</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.09848312447148405</v>
+        <v>-0.1049552367064456</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2519132640287374</v>
+        <v>0.1266531391210649</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.175309228336798e-12</v>
+        <v>0.1420941807495937</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0780872626614058</v>
+        <v>-0.1574313871462326</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.185087018765323</v>
+        <v>-0.02273794681604115</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.01396575522167032</v>
+        <v>0.1497344716567471</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01036402411504527</v>
+        <v>-0.006004673555879281</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.07345360030003803</v>
+        <v>-0.1250299344759726</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1964397770946492</v>
+        <v>0.1787221243939262</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.04518879857604378</v>
+        <v>0.2032729382121959</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02336346175054714</v>
+        <v>0.03503662228564737</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.00841339661408705</v>
+        <v>-0.03121418829183812</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.007118671161840619</v>
+        <v>0.1723459166242455</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.07576472869398242</v>
+        <v>-0.2076002733737087</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.05032615641202074</v>
+        <v>0.2555826428712966</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.1880285409710878</v>
+        <v>-0.02179777142599072</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004397927308157227</v>
+        <v>0.214953781091839</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.2144790038582241</v>
+        <v>0.143332271868045</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.02223250375553137</v>
+        <v>-0.07193026572716177</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1738755188880503</v>
+        <v>0.03619402716012324</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.1096488003139079</v>
+        <v>-0.06341465232420493</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1301212784596683</v>
+        <v>-0.1220290710947424</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.01854279967254182</v>
+        <v>0.2272611080266672</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1955912895394289</v>
+        <v>-0.03926113248237457</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001193350995277551</v>
+        <v>-0.0345421848009474</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.1090277126627539</v>
+        <v>-0.2067344884206651</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-9.26249914145034e-08</v>
+        <v>0.1657067276948397</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.1225531329532932</v>
+        <v>0.003341040622137198</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.1210830136140441</v>
+        <v>-0.09824142803766969</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.003992149179809911</v>
+        <v>-0.02679837906152298</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.2057318172892052</v>
+        <v>0.02076177017628884</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.03952253789878984</v>
+        <v>0.0002053716012535548</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0517978802769537</v>
+        <v>-0.01386959902127989</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1398990696187461</v>
+        <v>0.1790588997793817</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.2187034194620273</v>
+        <v>-0.1549675148070198</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.2165913851977678</v>
+        <v>0.1256689776034506</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1230860608803125</v>
+        <v>-0.0300156031494856</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001874959859419773</v>
+        <v>-0.02327916462088913</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.1104338768923869</v>
+        <v>-0.06404025711814637</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.08826556266649403</v>
+        <v>-0.1174026224017583</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1928397551976297</v>
+        <v>0.007937814068102959</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1525546586463894</v>
+        <v>0.007948289902696359</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.2016757023490214</v>
+        <v>0.05949857868667545</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1645461861996572</v>
+        <v>0.1101246412784747</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1362527567830195</v>
+        <v>0.08881326806655056</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.01556069141030343</v>
+        <v>0.1539899285722957</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.1678083749121017</v>
+        <v>0.05669840420725905</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.02089922019990999</v>
+        <v>-0.02275294404503887</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.1492137012464567</v>
+        <v>-0.01607936082334103</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.06865549950512505</v>
+        <v>1.358053000765438e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02982891377956441</v>
+        <v>-0.02755782768144947</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02587744582372708</v>
+        <v>0.132253043889684</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0380746129530735</v>
+        <v>-0.007710392955392232</v>
       </c>
       <c r="CA6" t="n">
-        <v>-2.746031663341799e-05</v>
+        <v>1.351187878077511e-06</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.05199527342954666</v>
+        <v>-0.004241431799947343</v>
       </c>
       <c r="CC6" t="n">
-        <v>-9.167337135453376e-06</v>
+        <v>-0.001456983727022834</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0005871973295102967</v>
+        <v>-0.1484574965084177</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.05649109436289207</v>
+        <v>0.06105450042851868</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.04192758225774266</v>
+        <v>-0.1204057562754461</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.005346614549505597</v>
+        <v>0.03026232718653201</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.04835252574793277</v>
+        <v>0.1627820985954096</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.2375538549004765</v>
+        <v>-0.2444469570896523</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.1841510068727287</v>
+        <v>-0.1409247402912006</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.419892098367013e-08</v>
+        <v>-0.003464344666605319</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.2007600004385621</v>
+        <v>-0.1224821146808556</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0001141635723209361</v>
+        <v>0.003186839048471032</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.01348908860184011</v>
+        <v>-0.05556384833075433</v>
       </c>
       <c r="CO6" t="n">
-        <v>4.64151871532067e-11</v>
+        <v>0.2018008951610965</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.209154272759337</v>
+        <v>-0.09593551328972219</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1942231899459366</v>
+        <v>-0.1581702180943038</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1716363899228047</v>
+        <v>0.1081213869474147</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.2067870773221791</v>
+        <v>0.02906815412340415</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.2079734617498984</v>
+        <v>-0.003608323508370462</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.07457197105938138</v>
+        <v>-0.001003982150085746</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.1897950781472561</v>
+        <v>0.03086870455377363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.01322113121660922</v>
+        <v>0.02022566314921301</v>
       </c>
       <c r="B7" t="n">
-        <v>0.007204876965418604</v>
+        <v>0.1764134395404076</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02161304380939646</v>
+        <v>-0.09416487925782216</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1709036752211812</v>
+        <v>-0.1235261237028142</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03425133959203424</v>
+        <v>0.01448361821557764</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08071468245261784</v>
+        <v>-0.188127877749582</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1417407264974103</v>
+        <v>9.45450698891309e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06412098926964105</v>
+        <v>0.1818372072103173</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02941496147474568</v>
+        <v>-0.02601833768476716</v>
       </c>
       <c r="J7" t="n">
-        <v>0.125197659495331</v>
+        <v>-0.1226629752192487</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1089861785472726</v>
+        <v>-0.2329140204938113</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1322653811966227</v>
+        <v>-0.1699082239025782</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2159115740831835</v>
+        <v>0.06435444858699331</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0538614962691239</v>
+        <v>-0.2231914380065475</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05321977350811427</v>
+        <v>-0.02835682035133846</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1884530826575153</v>
+        <v>-0.002852668456866512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1836931483498638</v>
+        <v>-0.1747397922382565</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.008458820639551648</v>
+        <v>0.002799737566041117</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1696501828938908</v>
+        <v>0.0283578509099242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2264059664054531</v>
+        <v>-0.2100956543141555</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02783877998134057</v>
+        <v>-0.007634080527049773</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1076290762587637</v>
+        <v>0.000196303184126527</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02935603444596951</v>
+        <v>0.09558174213057574</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2250423528140394</v>
+        <v>-0.2379383634113673</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06225802045241664</v>
+        <v>-0.1988675099814509</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1622499404663895</v>
+        <v>-5.130378452410426e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.14956020474416</v>
+        <v>-0.2202145447670241</v>
       </c>
       <c r="AB7" t="n">
-        <v>-6.43403161951984e-08</v>
+        <v>-0.173265243245927</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1070108889172624</v>
+        <v>-0.02842455007155084</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.119806393330157</v>
+        <v>-0.004973601687361678</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1990791237835409</v>
+        <v>0.2151585856973826</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.06151059717270461</v>
+        <v>-0.006238424889096883</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.1296977023735133</v>
+        <v>-0.0135244628676534</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.07358046369174892</v>
+        <v>-0.1466121025998422</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1039982302832573</v>
+        <v>-0.1065909542421284</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.101339052867552</v>
+        <v>-0.1007589376533449</v>
       </c>
       <c r="AK7" t="n">
-        <v>-2.380907227565106e-09</v>
+        <v>-0.1079003223717105</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.207280625176265</v>
+        <v>0.001561442575946038</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.01938180328333998</v>
+        <v>0.06941902269063752</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.02848300694968602</v>
+        <v>-0.0949238677309905</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1725849605924443</v>
+        <v>-0.09082560687676698</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1.356735933665272e-05</v>
+        <v>0.08876770137385148</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1365282187559018</v>
+        <v>-0.1920088249708754</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.02888814197811218</v>
+        <v>0.0001438128616421448</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.1396283289023486</v>
+        <v>-0.05313064523284986</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.2100550403182033</v>
+        <v>0.03719248895777018</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.05203712549073831</v>
+        <v>-0.01059463511929399</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.03022772399332735</v>
+        <v>0.2576398061932617</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.07659003197188048</v>
+        <v>0.03225223645546608</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.08090183345170543</v>
+        <v>-0.0003799539851048222</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.05789286882308689</v>
+        <v>0.1492949187964812</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.01775200958093217</v>
+        <v>-0.1760307872213931</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.04884735863737485</v>
+        <v>-0.1510822760870935</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.08898977443138346</v>
+        <v>-0.09999575158643696</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.007195942561445562</v>
+        <v>-0.3136479679877876</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.009456989609148257</v>
+        <v>-0.003153110797907383</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01109908637324697</v>
+        <v>0.0422604872696374</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0854925809507457</v>
+        <v>0.0004746081892242554</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1187882643834521</v>
+        <v>-0.2315282465449763</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.11797784055276</v>
+        <v>0.1209376433502052</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1508731219081557</v>
+        <v>0.1524363127141779</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.2173394579416776</v>
+        <v>-0.07863625182158317</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.54882204045841e-10</v>
+        <v>0.1380355098489967</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1689920816479129</v>
+        <v>0.03217148326381605</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.08468569392305635</v>
+        <v>-0.216414769425137</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.176734135202913</v>
+        <v>-0.03193680580059594</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.1912983752493506</v>
+        <v>0.09255342233267649</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.007187435669410858</v>
+        <v>6.959864904783609e-05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.1581656241805064</v>
+        <v>-0.04554714813435186</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.08475334594716274</v>
+        <v>-0.05413417631888824</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02694222704250641</v>
+        <v>0.1295908311801998</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.01336799473163795</v>
+        <v>-0.02494200937477484</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0001179717292665086</v>
+        <v>-0.01759837075860471</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.04190019032743325</v>
+        <v>-0.09803141062228853</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001930289849995186</v>
+        <v>7.883144253576621e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2300529030063317</v>
+        <v>-0.2140172416242824</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02785092937197146</v>
+        <v>-0.08082962256324988</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.2046425758998806</v>
+        <v>-0.1356889635427934</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.19387428494399e-06</v>
+        <v>-0.0031149896892988</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01690989745834221</v>
+        <v>-0.01240244797728698</v>
       </c>
       <c r="CC7" t="n">
-        <v>8.119218184054391e-11</v>
+        <v>0.06696806179440577</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.1259974834017812</v>
+        <v>-0.2715997771834388</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1084048169960757</v>
+        <v>-0.1287213009119137</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.2351379761079625</v>
+        <v>0.1016680490285084</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.2483474211766903</v>
+        <v>-0.05180506400069027</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.2550242188234316</v>
+        <v>0.1212733971293116</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.05691046044992272</v>
+        <v>-0.2359883524074448</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.2197644976557648</v>
+        <v>0.004564933412999152</v>
       </c>
       <c r="CK7" t="n">
-        <v>2.815480671140475e-08</v>
+        <v>0.0218466874957988</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.004070531357625863</v>
+        <v>-0.06284043660536817</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.000436770577907e-09</v>
+        <v>2.580104357816155e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.04004392102776825</v>
+        <v>1.792153751136792e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.01661248075802164</v>
+        <v>-0.2239381000216646</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.03793302185608882</v>
+        <v>-0.09691451907646217</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1201024178963852</v>
+        <v>0.141077169337923</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.03849125407448054</v>
+        <v>-0.2031209629940461</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.1086664251782602</v>
+        <v>0.04766822860779328</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1946967587761199</v>
+        <v>1.315603390793403e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.09805776469207073</v>
+        <v>0.2493955615263721</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.1941674702023835</v>
+        <v>0.1122881425841359</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
@@ -732,1814 +732,1814 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.0650095127821495</v>
+        <v>-0.2140510409570869</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1630669102941881</v>
+        <v>0.1212551522629641</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.539698749195595e-06</v>
+        <v>-0.02885652502208999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1545747142539464</v>
+        <v>0.01546669753349968</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1006837899595165</v>
+        <v>0.02816624555911692</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2216125158764755</v>
+        <v>0.0003392815168791163</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1942614750504184</v>
+        <v>-0.01127636795320766</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07332365587173732</v>
+        <v>-0.1486054045655804</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1020098032370384</v>
+        <v>0.1426144448187001</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1604086145594978</v>
+        <v>0.1426881910741367</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0338153867929662</v>
+        <v>0.0673567633634863</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1601980609737831</v>
+        <v>0.01859211617710081</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.187609044175817</v>
+        <v>-0.1469424892437396</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1158729266751317</v>
+        <v>-0.1916030129141663</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.09853437299218173</v>
+        <v>-0.1110782829827136</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1251367201650667</v>
+        <v>0.01574459637430184</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1437366475372206</v>
+        <v>-0.006316789947260585</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.06859068191156027</v>
+        <v>0.178454042786624</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2072944402125654</v>
+        <v>-0.05327397851838588</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1234136430654343</v>
+        <v>-0.03807073222906859</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.05542731712833387</v>
+        <v>-0.1758603176102459</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06414343640691283</v>
+        <v>0.1183554032406922</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03386767606924318</v>
+        <v>0.002314544606478837</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1009779737715781</v>
+        <v>-0.1007139419984857</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1107683938210098</v>
+        <v>0.08177401583148758</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05794781308096283</v>
+        <v>-0.0394637560088557</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02587080641743696</v>
+        <v>0.04630725137966091</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.08902312554303737</v>
+        <v>0.1021241990320885</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2206679278827498</v>
+        <v>0.1458202046875087</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.001555605675969562</v>
+        <v>-0.02355893832512629</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.08015413413380615</v>
+        <v>-0.2078974225353832</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0299073711234599</v>
+        <v>0.130677332122027</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.05451796887972863</v>
+        <v>0.04376340524988363</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02423449925659326</v>
+        <v>0.1231410246920658</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1585720188772259</v>
+        <v>0.0005249951159391069</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.006767319295815383</v>
+        <v>-0.07713051534808042</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1901071114161105</v>
+        <v>0.02626992237207834</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1392075259852637</v>
+        <v>-0.02695184344177427</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.09408774318568515</v>
+        <v>-0.1016494066592592</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.04602421455574521</v>
+        <v>-0.01751263728412372</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1249048656325981</v>
+        <v>-0.1115800187178002</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1202960208184117</v>
+        <v>-0.2427107910249345</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.1148579706807173</v>
+        <v>-0.05000115091311568</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.1037313284726938</v>
+        <v>-0.1059527423540017</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0623090637852768</v>
+        <v>-0.2453834916586427</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.2053787799573603</v>
+        <v>0.0001542930890584172</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1083595594679824</v>
+        <v>-0.05924352036121923</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.1097207125509886</v>
+        <v>0.2057972724393518</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09844624199187207</v>
+        <v>-0.006984593327784948</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.0003498180729842019</v>
+        <v>-0.003719819511727282</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.03858051325145134</v>
+        <v>0.02830289187765056</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.04895600184754943</v>
+        <v>0.1232189629747345</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.09330600920802147</v>
+        <v>-0.1154265794312637</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.01456908884706475</v>
+        <v>0.1018480217712891</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.08981961007436687</v>
+        <v>3.023774041338205e-05</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.005122529095361707</v>
+        <v>0.2007940469817002</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.04818791057702902</v>
+        <v>-0.03737359173150086</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01789229978575759</v>
+        <v>0.03016874797663875</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1087888452031312</v>
+        <v>0.1674489457536177</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.2150954960806389</v>
+        <v>-0.05794900912564504</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1774705471959754</v>
+        <v>-0.1204826939194294</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.1160187348825773</v>
+        <v>0.1613029023758395</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0663332255748095</v>
+        <v>-0.02231561602913743</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.02907699843372174</v>
+        <v>-0.02747969567535952</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.128249011168787</v>
+        <v>-0.0728103882218009</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.04872435406360103</v>
+        <v>0.2176586405973596</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.07187989965935022</v>
+        <v>0.01550604145475405</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.001282401638263761</v>
+        <v>0.04698364910756438</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1217183481143771</v>
+        <v>0.2489536778729002</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.06621472705762271</v>
+        <v>-0.050105124938032</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1296161261765075</v>
+        <v>0.1167957383565914</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.06350896041663311</v>
+        <v>-0.08399965746863329</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1731801956550992</v>
+        <v>0.2251544221835248</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.01335922099316914</v>
+        <v>-0.02648542370846593</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.06654285324367977</v>
+        <v>0.07922236846332031</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.1517768250292516</v>
+        <v>0.04683194868380562</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.05273614377190336</v>
+        <v>0.09662781146644039</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.1308186566264896</v>
+        <v>-0.09395230156385892</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0002086932397401231</v>
+        <v>0.1079587234858431</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.03995720776582944</v>
+        <v>-0.1577888063116089</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.06027620788899413</v>
+        <v>0.03347678961870954</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.151717610486308</v>
+        <v>-0.1233798106888512</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1571622933052727</v>
+        <v>-0.04333966807613053</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.0642817399558217</v>
+        <v>-0.0739189974545383</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.07333535703652315</v>
+        <v>-0.1074080879339515</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.06632901467990274</v>
+        <v>0.073634141512589</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.2466438167655948</v>
+        <v>0.04304001320690418</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1567966541465195</v>
+        <v>0.109835610384493</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.09595109816794033</v>
+        <v>0.1267011387495757</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1102820435413953</v>
+        <v>0.1299061478197307</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.001010525050066213</v>
+        <v>0.1001392336904723</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.008455541147542227</v>
+        <v>-0.07955350485608809</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.09505791885038307</v>
+        <v>-0.09275281549841659</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.04385982011392833</v>
+        <v>-0.006948498004167361</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.104942524816108</v>
+        <v>-0.1514798124814044</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.2220937545807433</v>
+        <v>0.00688387402410257</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.03411146037730215</v>
+        <v>-0.09982375477388687</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.000195305988395338</v>
+        <v>-0.1285551442235661</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1742397089348392</v>
+        <v>0.09287046649326254</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.03274528335049792</v>
+        <v>-0.01228135369972552</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03119520546878109</v>
+        <v>0.2413952931974666</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05453828941045789</v>
+        <v>-0.0007272847303655061</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.06375999550855412</v>
+        <v>-0.04734157472287915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2317561190642877</v>
+        <v>0.1985783031412945</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2375617017432221</v>
+        <v>-0.1244014108084694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1086257218248655</v>
+        <v>-0.1923204838454803</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2376190986556549</v>
+        <v>0.1594518292501265</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2352161927611187</v>
+        <v>-0.215965169142651</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2281857475459848</v>
+        <v>0.1209091010926581</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1975115056302851</v>
+        <v>0.1452914017994</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2392577970659195</v>
+        <v>-0.11214410002908</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1934402739207028</v>
+        <v>0.2146534180147024</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1813287629922346</v>
+        <v>0.02721250526259281</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07272068272962744</v>
+        <v>-0.0777832003782393</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.03926685273979127</v>
+        <v>1.436248604509836e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1523525462168346</v>
+        <v>-0.03239579255493744</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2403290508438006</v>
+        <v>-0.1964130791100469</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.08690488436777306</v>
+        <v>-0.0006488254156385921</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1196122778107567</v>
+        <v>0.1087378835181618</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01179221896514384</v>
+        <v>-0.1921084473059164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001620666541513278</v>
+        <v>0.05940840608565121</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.09959936660607181</v>
+        <v>-0.01396340219474721</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05902080386386828</v>
+        <v>-0.05950018976687241</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2187102848360645</v>
+        <v>0.1162653637210322</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2233493037555076</v>
+        <v>-0.02912667787640525</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.06235092228304e-06</v>
+        <v>0.1850427076990078</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2059827396833024</v>
+        <v>-0.1195422582577109</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1385083588148613</v>
+        <v>0.1056351708190942</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.08473528926712558</v>
+        <v>-0.1846423655655838</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.008499216908993726</v>
+        <v>-0.1416098021449712</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1307988280390748</v>
+        <v>0.193511180485926</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02736812711998397</v>
+        <v>-0.02476542617350473</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.04329355812861513</v>
+        <v>-0.1377911482630401</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.1427439602662426</v>
+        <v>-2.316494621847061e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1057761678307341</v>
+        <v>0.09441327785375075</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.01319147622269065</v>
+        <v>-0.003768780067026121</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1262573648435981</v>
+        <v>-0.2033397082879621</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.1383588825744323</v>
+        <v>-0.1801250836583723</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1397518764108172</v>
+        <v>0.04222853229569667</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.1086146742579395</v>
+        <v>0.01981613880527106</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.05214649177087152</v>
+        <v>-0.02133188980564286</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08302392115339642</v>
+        <v>0.2046356858311762</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.162501031307067</v>
+        <v>-0.00941965645794765</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001590560619028915</v>
+        <v>0.2198038613145837</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.2238517576270987</v>
+        <v>0.1436404474620546</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.06603605088309963</v>
+        <v>0.000492372735154361</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1121311388762331</v>
+        <v>0.1097675451504837</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.153706689623947</v>
+        <v>-0.1801952326041966</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.07083839372854907</v>
+        <v>-0.1053661782953221</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1005591694425817</v>
+        <v>0.1820240716163141</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1940395884827074</v>
+        <v>-0.1174440081346958</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.1543779664168168</v>
+        <v>0.1738836785853622</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08627624847153828</v>
+        <v>0.1543135340962385</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.05065279388868678</v>
+        <v>-0.006775118112334685</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2495761447314426</v>
+        <v>-0.02343701724155176</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.08503900522103415</v>
+        <v>0.1233496247218267</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.06419444574224105</v>
+        <v>0.05215830135121734</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.02364752468964018</v>
+        <v>-0.009372402676213006</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1194635548354593</v>
+        <v>0.02903444731219474</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.1859881249896693</v>
+        <v>-0.03871367396170984</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.211792904795831</v>
+        <v>-0.02649291662863867</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.181831760702864</v>
+        <v>0.04722720759986174</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0619007442467441</v>
+        <v>0.1749413167406775</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.2059874369994993</v>
+        <v>-0.03491081946313752</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1567162287052302</v>
+        <v>-0.02944791617668045</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.01768233964885746</v>
+        <v>0.01209121009223257</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.08606715501448396</v>
+        <v>0.09513721857640832</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.08989315594141291</v>
+        <v>0.196655045590397</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06463601447548735</v>
+        <v>-0.174955483111418</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1292094672946035</v>
+        <v>0.03597568099242371</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.09003198300276526</v>
+        <v>0.223999707045659</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.05250491933874606</v>
+        <v>0.07679129104377186</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1797790699825099</v>
+        <v>0.07563684196881269</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.1066216285385268</v>
+        <v>-0.0653936967104536</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.08528597869940471</v>
+        <v>0.2112349633649015</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.04791848899268621</v>
+        <v>0.002949876234078962</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.07478960973426867</v>
+        <v>0.02635315351893631</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.08662428021241814</v>
+        <v>0.1649257313803912</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.01401113212213608</v>
+        <v>-0.1766945655086288</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.06379124777058717</v>
+        <v>0.1443410767290657</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.03093516170377981</v>
+        <v>0.196965809003377</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.2132087912911065</v>
+        <v>-0.1200909001233068</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.07712532488449962</v>
+        <v>-0.08149392209504275</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1770496942314913</v>
+        <v>0.2188585208170198</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1505873629698374</v>
+        <v>-0.1193230331675897</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.08587463899088228</v>
+        <v>-0.02617395229647053</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.2299452914296656</v>
+        <v>-0.1883697172838435</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1699168080028989</v>
+        <v>0.1817582668134557</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.03252890562652494</v>
+        <v>-0.2060716542523809</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1340053448465273</v>
+        <v>0.1593389668953724</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.002884511461070465</v>
+        <v>-0.07474414963110593</v>
       </c>
       <c r="CN3" t="n">
-        <v>-2.662261469589017e-05</v>
+        <v>-0.03076441686132975</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.2270666051529409</v>
+        <v>-0.1288093723360188</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.002581353052225721</v>
+        <v>-0.02286469420585365</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1175671119787897</v>
+        <v>0.1215421771488854</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0742350572167562</v>
+        <v>-0.02194758761943003</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.1704858897082024</v>
+        <v>-0.02555217057853949</v>
       </c>
       <c r="CT3" t="n">
-        <v>-4.041800679597918e-05</v>
+        <v>-0.0115732113511161</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1495729386857374</v>
+        <v>0.09671574316269661</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.1444808653544986</v>
+        <v>-0.0432172505707083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.09501781419195775</v>
+        <v>-0.142453354463209</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1138904471476487</v>
+        <v>-0.1099156887051409</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.40138304418787e-06</v>
+        <v>-0.09615942120785732</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001249723363203378</v>
+        <v>0.07350089091530389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05642589678164112</v>
+        <v>-0.0002232590793418531</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1121806629252453</v>
+        <v>-0.06947960426977624</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.01458226951781372</v>
+        <v>0.1380801564988187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1831143513143489</v>
+        <v>0.05828437477645953</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1656356817848606</v>
+        <v>-0.1139755916202918</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1960732748996663</v>
+        <v>0.2085847825319946</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1281980483050676</v>
+        <v>0.131964503626235</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08907105877230269</v>
+        <v>-0.1294959106691239</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1552538348314348</v>
+        <v>-0.006123717767882834</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2453306432244059</v>
+        <v>-0.08891885988496556</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0338417236432365</v>
+        <v>-0.06838572798643341</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02418669660465718</v>
+        <v>-0.09121318915216771</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.134545776146368</v>
+        <v>0.1892696008342807</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.05037031548662523</v>
+        <v>-0.1508537178522268</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06565947728528181</v>
+        <v>-0.1888813684690637</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1055930060112348</v>
+        <v>0.1768722354106719</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1016962785025836</v>
+        <v>0.1393825801333634</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.000807821901244148</v>
+        <v>-0.08819486082374101</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03098766968835787</v>
+        <v>-0.05052003571831487</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1454580123612128</v>
+        <v>-0.2182067283425804</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1411599763108849</v>
+        <v>-0.002604586665320554</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.02670350112988821</v>
+        <v>0.06967624166026125</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.04408077671298922</v>
+        <v>-0.03201896574055856</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.08671681642743607</v>
+        <v>0.07615289184056255</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.2198707688373748</v>
+        <v>0.1162105378588452</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.09610872002527918</v>
+        <v>0.1266103248183638</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1207615152048892</v>
+        <v>-0.1167663062407043</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02477469081485355</v>
+        <v>-0.06651854835394314</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.13791278027459</v>
+        <v>-0.144414946644368</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.06085036366942632</v>
+        <v>-0.02116664282616083</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.01525742687676825</v>
+        <v>0.1551362056564753</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.02941684119181699</v>
+        <v>0.06832064581669052</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1329479688955668</v>
+        <v>0.2407174744565285</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01064237249885369</v>
+        <v>0.08926899603852738</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.1609600547367056</v>
+        <v>0.2546666564112029</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.1425025542281628</v>
+        <v>0.1404226589754693</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.04152748100418093</v>
+        <v>-0.01891926341632147</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1723889717889768</v>
+        <v>0.1560706914350465</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2220403758288574</v>
+        <v>-0.06194211863295583</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.07889144179355405</v>
+        <v>0.1378885795275923</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.155060923112196</v>
+        <v>0.02740377183445277</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.1019864319421312</v>
+        <v>-0.08862573377994717</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.0713400938227222</v>
+        <v>-0.08579790075800986</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2302107917418741</v>
+        <v>0.2120233547811152</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.05902269070646989</v>
+        <v>-0.01767996807191046</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.09616476712993068</v>
+        <v>0.1284295811868583</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1720417039406072</v>
+        <v>-0.117682187246209</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.01068530382292025</v>
+        <v>0.1210405363511782</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.09293059570446784</v>
+        <v>0.2200548584728563</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.649635677079004e-06</v>
+        <v>0.07148274096041463</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.07686417762330013</v>
+        <v>-0.003494424795588218</v>
       </c>
       <c r="BD4" t="n">
-        <v>-5.189794820853525e-07</v>
+        <v>-0.07909770985421845</v>
       </c>
       <c r="BE4" t="n">
-        <v>-2.286672902397692e-07</v>
+        <v>-0.02266705277237226</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01536147967683698</v>
+        <v>0.1062120361732347</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1064190777552721</v>
+        <v>-0.2257669161316275</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.2290708626700839</v>
+        <v>-0.03976237892383089</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0543760679901078</v>
+        <v>-0.09943994889972634</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.03158648015893108</v>
+        <v>0.2238594487117017</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.06955094663856611</v>
+        <v>0.1258666533881992</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.07486062688706403</v>
+        <v>-0.1744382619284514</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.1848006468326213</v>
+        <v>-8.36091879180333e-07</v>
       </c>
       <c r="BN4" t="n">
-        <v>-8.996177734170057e-06</v>
+        <v>-0.05645426805187735</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.1949937628856506</v>
+        <v>-0.08785074832340763</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.02862200300165913</v>
+        <v>-0.1726813904865517</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.03031676093053352</v>
+        <v>0.244897172606865</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1283233600089602</v>
+        <v>0.187018453887358</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1673309386110468</v>
+        <v>0.1205119207774365</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.04531013323211822</v>
+        <v>0.08343717702987341</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.1600674108037209</v>
+        <v>-0.04899086489588974</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.009339728953641416</v>
+        <v>0.2057182848499734</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.02621130832453275</v>
+        <v>0.171708432339698</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.184526791546963</v>
+        <v>0.007578947306995909</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.2274657856537918</v>
+        <v>0.1872979203858117</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1916344356910789</v>
+        <v>0.01564185226412145</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0.03535742148159968</v>
+        <v>0.135045437910221</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0.001893296899297594</v>
+        <v>0.02677063206562924</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0.04283117496483914</v>
+        <v>0.1134373175556764</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.1991402573909706</v>
+        <v>0.07056080697532267</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.07337572331301979</v>
+        <v>-0.0233288342247261</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0.2066986871481866</v>
+        <v>-0.1005048044032981</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.1115037713378876</v>
+        <v>0.006520868619628781</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.200345964677312</v>
+        <v>-0.02866936877040388</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.08127228664792099</v>
+        <v>-0.0737082149330653</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1098106679131062</v>
+        <v>0.03845621884179094</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.03519191496940405</v>
+        <v>0.07961621946431888</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.177129336983915</v>
+        <v>-0.1629416383403399</v>
       </c>
       <c r="CM4" t="n">
-        <v>-8.068840258492895e-07</v>
+        <v>-0.111521523752145</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.004524654024415712</v>
+        <v>0.07019424639329544</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.07652786645402841</v>
+        <v>0.1763068398194647</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.06577279864043899</v>
+        <v>-0.007930429302355423</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1662030042380093</v>
+        <v>-0.1376334379699952</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1310120313495333</v>
+        <v>-0.009283400227202542</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1664178521305204</v>
+        <v>0.09659655740990984</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0.03096324335603241</v>
+        <v>-0.06965293412069222</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.2098387359458961</v>
+        <v>-0.2222121375504979</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.125034879772089</v>
+        <v>-0.01384090033203071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2261320700717534</v>
+        <v>0.1361157188518375</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1815073024891113</v>
+        <v>-0.0001019957605593627</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004442477955449186</v>
+        <v>0.2077384444674999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2269914066815974</v>
+        <v>-0.06850479726477816</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07852746653815038</v>
+        <v>-0.01898189954906079</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2198826610281876</v>
+        <v>0.132544435379679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2185920831726928</v>
+        <v>0.05919669670234564</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002915921977387343</v>
+        <v>0.1342999580842771</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2152204016016696</v>
+        <v>-0.1632057113914009</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01219363171577638</v>
+        <v>0.1682834986062694</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.158074753246879</v>
+        <v>0.05902121073110676</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04377570536062304</v>
+        <v>-0.1097788722230109</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2045797397085301</v>
+        <v>-0.2440887596165592</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004202348279729898</v>
+        <v>-0.08634817431926436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1339898924352934</v>
+        <v>-0.07344957058579299</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2059809581356347</v>
+        <v>-0.0003020894014386281</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01936323680428024</v>
+        <v>-0.1971216750473679</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03488815058204871</v>
+        <v>-0.1640933810015468</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.005264671911670426</v>
+        <v>0.1290167133476586</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2310714302475455</v>
+        <v>-0.1066382824680625</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07633292904883759</v>
+        <v>0.06489850138484295</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07935253116665533</v>
+        <v>-0.1260600940546143</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1970253332892179</v>
+        <v>-0.001628726736338265</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1814165284775302</v>
+        <v>-0.06623284673937818</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1755382499551779</v>
+        <v>0.124115390973449</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00293425384594352</v>
+        <v>0.03450539108609788</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.06477625919928179</v>
+        <v>0.002637065183642222</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2004534571780427</v>
+        <v>0.002613662696703659</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06713542012748036</v>
+        <v>0.0993512882007353</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.03332726500276095</v>
+        <v>-0.2272666480698855</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1707750460211278</v>
+        <v>0.01444262551661058</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0004036293135947124</v>
+        <v>0.02084396538229245</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01579452944261377</v>
+        <v>0.1161130676042686</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2340565095940542</v>
+        <v>-0.04768646712170437</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1799144737718006</v>
+        <v>0.1245764707513159</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.02407868291285258</v>
+        <v>-0.1516015249581898</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.1852381992665146</v>
+        <v>0.2417044020677474</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1633449273608423</v>
+        <v>-0.2110172578391361</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1921525759309105</v>
+        <v>-0.08621617395145983</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0143370526500892</v>
+        <v>0.1922048820726282</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.01582884048439632</v>
+        <v>0.1215235326746915</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.07070892136993191</v>
+        <v>0.06349098997627947</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004103463837791639</v>
+        <v>0.005184684196008638</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.04582414974018842</v>
+        <v>0.1048523912996279</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.1526070997585837</v>
+        <v>0.008233357107557699</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01602266461008885</v>
+        <v>1.446691201197367e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1284073823816484</v>
+        <v>0.2063873811965163</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1388836218152615</v>
+        <v>0.2443460426391759</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02293654136790474</v>
+        <v>-0.1037434383596235</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001004687076766759</v>
+        <v>0.0114249469782372</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.09929951764222363</v>
+        <v>0.01329484474553737</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.1406670081777398</v>
+        <v>-0.17814167739248</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.1311066581136189</v>
+        <v>-0.2464478668583145</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.05854293634520058</v>
+        <v>-0.2192749882953168</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.1099506933363389</v>
+        <v>-0.04160307345228356</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.06755280140061791</v>
+        <v>-0.08446748737625369</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.05787324500867525</v>
+        <v>0.139355451237806</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.003667474534957107</v>
+        <v>-0.01449237774077976</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1238345836543889</v>
+        <v>0.111754438246424</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.1417247094495514</v>
+        <v>0.1241961030202866</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.161895446738979</v>
+        <v>0.09011227191067257</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.06947601207145619</v>
+        <v>-0.002942884377870269</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.02479006923027341</v>
+        <v>-0.202922036915568</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002190555323842778</v>
+        <v>0.08035741816898849</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.06333946241566218</v>
+        <v>-0.06141889072132212</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.04777842196488042</v>
+        <v>0.1582006645170096</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.004045446943631141</v>
+        <v>0.1304266738452905</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1034134689789705</v>
+        <v>0.2409380783130067</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.2124980917595456</v>
+        <v>-0.01514281039618009</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.1957892062458037</v>
+        <v>-0.1881116453352279</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.1964647515366472</v>
+        <v>0.1451398875590292</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.07943701362415663</v>
+        <v>-0.0861423189901751</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.08340041952272123</v>
+        <v>0.1294843337059318</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.180580873570866e-05</v>
+        <v>0.128152412081362</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0009629820730711208</v>
+        <v>-0.02739865992581813</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.2312768102039145</v>
+        <v>0.2285005724222054</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.2141203618549144</v>
+        <v>-0.2282350551174712</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.2023602467586924</v>
+        <v>0.2101736513679894</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.008260605605144921</v>
+        <v>-0.02545005933967012</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001024579744018268</v>
+        <v>0.01496552123067697</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.04985530286270144</v>
+        <v>-0.2502127550464998</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1948657764247243</v>
+        <v>-0.09479901978356896</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.2313364196959402</v>
+        <v>-0.04423599394897833</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.222271309190945</v>
+        <v>-0.2184061589390281</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.2016544748197904</v>
+        <v>0.1267701722770685</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.02458534960029615</v>
+        <v>0.1309092449498487</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.05866572572225832</v>
+        <v>0.1822536210313227</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1173818849418641</v>
+        <v>0.17790241278125</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.00689269340349811</v>
+        <v>-0.2268342849956418</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.1941912545643686</v>
+        <v>0.173032578586914</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.04622180821213522</v>
+        <v>-0.008630057330209549</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.1008898870098774</v>
+        <v>-0.04676660158663019</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.1375533193785859</v>
+        <v>0.1485194157504702</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1194613415929378</v>
+        <v>-0.09112245376775169</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1546522523071668</v>
+        <v>0.1623777771093561</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.05274272625808182</v>
+        <v>0.09807723257600516</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1580214248856845</v>
+        <v>-0.07569666097702203</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0002639336045600893</v>
+        <v>-0.03725604847034509</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1022254003487066</v>
+        <v>-0.1695211742049113</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.2279260508147205</v>
+        <v>-0.06651685773049024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.01321694901044968</v>
+        <v>0.006240892045355562</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1291495474963885</v>
+        <v>0.0003451138501616207</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.009338843998996104</v>
+        <v>-0.05846737393132122</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09758549982235988</v>
+        <v>0.08556936396412033</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1899709712988017</v>
+        <v>-0.07294587441620703</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2076539621767808</v>
+        <v>0.2180642086982937</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.162835076570134</v>
+        <v>0.08421162973541847</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01908526804444344</v>
+        <v>0.1412899499474544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05659184863102</v>
+        <v>0.1026302674444111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1153790556332604</v>
+        <v>0.1621537298708889</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1887235121419928</v>
+        <v>-0.09067485830760942</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1577904557779105</v>
+        <v>0.0558567849554406</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1232197238322278</v>
+        <v>-0.02585903326253416</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1517497353192374</v>
+        <v>0.1394632460622994</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1571272649391423</v>
+        <v>-0.002356304869388284</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04163643480113024</v>
+        <v>-0.001319186547986263</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1336793374258129</v>
+        <v>0.0574831165716464</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0008471337609780882</v>
+        <v>0.1283541489099372</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2020341387364801</v>
+        <v>0.1041013092343669</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.164187383858232</v>
+        <v>-0.02924193053748227</v>
       </c>
       <c r="U6" t="n">
-        <v>6.07746163914118e-07</v>
+        <v>-0.162348850669317</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.07982595211151809</v>
+        <v>5.685249819998286e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.15215159846458</v>
+        <v>-0.1098006901830353</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08460809824649181</v>
+        <v>0.1750514550171406</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02198297863485373</v>
+        <v>-0.1195474232136388</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1049552367064456</v>
+        <v>-0.0103721493826118</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1266531391210649</v>
+        <v>0.07503583215420551</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1420941807495937</v>
+        <v>-0.1101995987206786</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1574313871462326</v>
+        <v>0.01928294054107571</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.02273794681604115</v>
+        <v>0.0869520779142396</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1497344716567471</v>
+        <v>0.2183744136493732</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006004673555879281</v>
+        <v>0.01991216165415454</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.1250299344759726</v>
+        <v>0.1201043577274704</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1787221243939262</v>
+        <v>-0.03827266983823407</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2032729382121959</v>
+        <v>-0.2333146460216348</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.03503662228564737</v>
+        <v>0.09654725413516729</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.03121418829183812</v>
+        <v>-0.1961845448778349</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1723459166242455</v>
+        <v>-0.06475839130973056</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.2076002733737087</v>
+        <v>-0.08228004977133965</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.2555826428712966</v>
+        <v>-0.115961755248247</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02179777142599072</v>
+        <v>-0.1039271453238811</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.214953781091839</v>
+        <v>0.01583580249289785</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.143332271868045</v>
+        <v>-0.05654035729477759</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.07193026572716177</v>
+        <v>0.09146082906925386</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.03619402716012324</v>
+        <v>0.2348242584864058</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.06341465232420493</v>
+        <v>-0.07626334433556563</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.1220290710947424</v>
+        <v>0.02383676364244334</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2272611080266672</v>
+        <v>-0.04139995513088328</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.03926113248237457</v>
+        <v>-0.005892405433521675</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0345421848009474</v>
+        <v>0.02922551570226636</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.2067344884206651</v>
+        <v>-0.02398355370635331</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1657067276948397</v>
+        <v>0.01212564641553114</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.003341040622137198</v>
+        <v>0.05946705025789551</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.09824142803766969</v>
+        <v>0.17515578186343</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.02679837906152298</v>
+        <v>-0.03661967947969598</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02076177017628884</v>
+        <v>0.07674009479511847</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0002053716012535548</v>
+        <v>-0.1470029866925688</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.01386959902127989</v>
+        <v>0.1663041066538782</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1790588997793817</v>
+        <v>0.1885256808571456</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.1549675148070198</v>
+        <v>-0.03214644542525912</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1256689776034506</v>
+        <v>-0.1009469141588248</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0300156031494856</v>
+        <v>-0.1365665224472098</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.02327916462088913</v>
+        <v>0.01664673513273315</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.06404025711814637</v>
+        <v>0.03345486430414576</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1174026224017583</v>
+        <v>-0.0961265746318002</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.007937814068102959</v>
+        <v>-0.1628405169317243</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.007948289902696359</v>
+        <v>-0.1813947228255312</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.05949857868667545</v>
+        <v>-0.09748635497023861</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1101246412784747</v>
+        <v>0.2044336970193356</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.08881326806655056</v>
+        <v>-0.2302563997727333</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1539899285722957</v>
+        <v>-0.1253408983957321</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.05669840420725905</v>
+        <v>-0.03088565068781423</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.02275294404503887</v>
+        <v>-0.1670846170396304</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.01607936082334103</v>
+        <v>-0.09329198544259411</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.358053000765438e-06</v>
+        <v>0.1547402700435385</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02755782768144947</v>
+        <v>-0.06190357107106241</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.132253043889684</v>
+        <v>-0.2242944300024786</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.007710392955392232</v>
+        <v>0.2240436155332787</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.351187878077511e-06</v>
+        <v>0.02892853920074518</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.004241431799947343</v>
+        <v>-0.001256002838011201</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001456983727022834</v>
+        <v>-0.1148300648930835</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.1484574965084177</v>
+        <v>0.09341348480015431</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.06105450042851868</v>
+        <v>0.03222735525075174</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.1204057562754461</v>
+        <v>-0.05338883877497648</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.03026232718653201</v>
+        <v>0.1234605127462324</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.1627820985954096</v>
+        <v>-0.2446406341955429</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.2444469570896523</v>
+        <v>0.1796320980346844</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.1409247402912006</v>
+        <v>0.04628970385793001</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.003464344666605319</v>
+        <v>-0.1594478019468034</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.1224821146808556</v>
+        <v>0.04885136045103941</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.003186839048471032</v>
+        <v>-0.07406273587161168</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.05556384833075433</v>
+        <v>0.05331970794494567</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.2018008951610965</v>
+        <v>0.1513552743478699</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.09593551328972219</v>
+        <v>0.0001184105863254286</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1581702180943038</v>
+        <v>-0.1994365601666291</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1081213869474147</v>
+        <v>-0.05099462076434234</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.02906815412340415</v>
+        <v>0.00430356830744289</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.003608323508370462</v>
+        <v>0.00156666716388089</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.001003982150085746</v>
+        <v>-0.02602766294792224</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.03086870455377363</v>
+        <v>-0.03042442504616875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.02022566314921301</v>
+        <v>0.1381370831242464</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1764134395404076</v>
+        <v>-0.001501870027146861</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.09416487925782216</v>
+        <v>0.1466580665861645</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1235261237028142</v>
+        <v>0.08911456348150691</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01448361821557764</v>
+        <v>-0.05275543643241383</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.188127877749582</v>
+        <v>-0.06389038073575287</v>
       </c>
       <c r="G7" t="n">
-        <v>9.45450698891309e-07</v>
+        <v>-0.007615352946495371</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1818372072103173</v>
+        <v>0.226427503290503</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02601833768476716</v>
+        <v>0.03341050519625569</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1226629752192487</v>
+        <v>-0.06869782328794624</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2329140204938113</v>
+        <v>0.008032980570541285</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1699082239025782</v>
+        <v>0.06994028339526943</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06435444858699331</v>
+        <v>0.08160547723437317</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2231914380065475</v>
+        <v>-0.03564083969658108</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02835682035133846</v>
+        <v>0.07421212419150305</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.002852668456866512</v>
+        <v>0.1034992235598471</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1747397922382565</v>
+        <v>0.2423349653398177</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002799737566041117</v>
+        <v>0.1605227560384187</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0283578509099242</v>
+        <v>-0.1631142463469935</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2100956543141555</v>
+        <v>0.2088498900333802</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.007634080527049773</v>
+        <v>0.04043116261452476</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000196303184126527</v>
+        <v>0.07128867556298402</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09558174213057574</v>
+        <v>0.009431418989349441</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2379383634113673</v>
+        <v>-0.1043084455383352</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1988675099814509</v>
+        <v>-0.0279453450515104</v>
       </c>
       <c r="Z7" t="n">
-        <v>-5.130378452410426e-05</v>
+        <v>-0.130726635142719</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2202145447670241</v>
+        <v>-0.03090762472805387</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.173265243245927</v>
+        <v>0.05638218604254575</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.02842455007155084</v>
+        <v>-0.0553760113946276</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.004973601687361678</v>
+        <v>-0.2069778814993569</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2151585856973826</v>
+        <v>-0.1349727812213321</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.006238424889096883</v>
+        <v>0.1343263382245559</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0135244628676534</v>
+        <v>0.04410573490814121</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1466121025998422</v>
+        <v>-0.02112301553524352</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1065909542421284</v>
+        <v>-0.04816873837663363</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.1007589376533449</v>
+        <v>0.09393078268884335</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.1079003223717105</v>
+        <v>0.09372349383749126</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.001561442575946038</v>
+        <v>-0.08527423394410859</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.06941902269063752</v>
+        <v>-0.07364483882969883</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0949238677309905</v>
+        <v>0.2320896903482425</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.09082560687676698</v>
+        <v>0.0004720186169337314</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08876770137385148</v>
+        <v>-0.169222872823061</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.1920088249708754</v>
+        <v>0.04563351608493135</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001438128616421448</v>
+        <v>0.06815631750687473</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.05313064523284986</v>
+        <v>0.1408112554516583</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.03719248895777018</v>
+        <v>-0.01785465699468268</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.01059463511929399</v>
+        <v>-0.1649742015820245</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2576398061932617</v>
+        <v>0.02254399619538603</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03225223645546608</v>
+        <v>-0.1081120647027511</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0003799539851048222</v>
+        <v>-0.2241727171594479</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.1492949187964812</v>
+        <v>0.00529584132684268</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.1760307872213931</v>
+        <v>-0.1959494050571841</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.1510822760870935</v>
+        <v>-0.1878826156112034</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.09999575158643696</v>
+        <v>0.07062997910641355</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.3136479679877876</v>
+        <v>-0.02414166401982852</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.003153110797907383</v>
+        <v>-0.07380139344644461</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0422604872696374</v>
+        <v>0.1617097760900207</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0004746081892242554</v>
+        <v>0.04414883694791666</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2315282465449763</v>
+        <v>0.1983918701814464</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1209376433502052</v>
+        <v>-0.007646041786635422</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1524363127141779</v>
+        <v>0.02620910670322654</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.07863625182158317</v>
+        <v>-0.1538252984750627</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1380355098489967</v>
+        <v>-0.03843204643067068</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.03217148326381605</v>
+        <v>-0.06066642923310407</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.216414769425137</v>
+        <v>0.09962899228525038</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.03193680580059594</v>
+        <v>0.2174003237249882</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.09255342233267649</v>
+        <v>-0.07131937061583221</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.959864904783609e-05</v>
+        <v>-0.1408680748282526</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.04554714813435186</v>
+        <v>0.1079059818249981</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.05413417631888824</v>
+        <v>0.03162549581689628</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1295908311801998</v>
+        <v>-0.001918656896558472</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.02494200937477484</v>
+        <v>-0.192738841067093</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.01759837075860471</v>
+        <v>0.003839835181892055</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.09803141062228853</v>
+        <v>0.1509940593321022</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.883144253576621e-06</v>
+        <v>0.02174516619482771</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.2140172416242824</v>
+        <v>-0.1565115488974462</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.08082962256324988</v>
+        <v>0.233543686022493</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.1356889635427934</v>
+        <v>-0.2203469431982842</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0031149896892988</v>
+        <v>0.05089413871576754</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.01240244797728698</v>
+        <v>-0.05565027319702965</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.06696806179440577</v>
+        <v>-0.002273294282384027</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.2715997771834388</v>
+        <v>-0.2106659270329126</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1287213009119137</v>
+        <v>0.01817411686662188</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1016680490285084</v>
+        <v>-0.1218282141582196</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.05180506400069027</v>
+        <v>0.2101778621076606</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.1212733971293116</v>
+        <v>-0.0579205423730872</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.2359883524074448</v>
+        <v>0.03223479410862651</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.004564933412999152</v>
+        <v>0.05058982868307143</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0218466874957988</v>
+        <v>-0.05511614980910159</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.06284043660536817</v>
+        <v>0.05874886077057042</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.580104357816155e-06</v>
+        <v>0.1185662275885931</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.792153751136792e-06</v>
+        <v>-0.1764089448367635</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.2239381000216646</v>
+        <v>-0.2217058318046127</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.09691451907646217</v>
+        <v>-0.007118730588992476</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.141077169337923</v>
+        <v>0.001504087071130237</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.2031209629940461</v>
+        <v>-0.01772736280079639</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.04766822860779328</v>
+        <v>0.1786638929289368</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.315603390793403e-06</v>
+        <v>0.002837534394789219</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.2493955615263721</v>
+        <v>-0.09454896175739637</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.1122881425841359</v>
+        <v>0.05947936732606422</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
@@ -732,1814 +732,1814 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.2140510409570869</v>
+        <v>0.01206295710363183</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1212551522629641</v>
+        <v>-0.1906464965721179</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02885652502208999</v>
+        <v>0.008734171420486282</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01546669753349968</v>
+        <v>-0.1839908017585135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02816624555911692</v>
+        <v>0.2572627645813086</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0003392815168791163</v>
+        <v>-0.04006759442028091</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01127636795320766</v>
+        <v>0.1751846841411333</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1486054045655804</v>
+        <v>0.1574141518199982</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1426144448187001</v>
+        <v>-0.156626153672333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1426881910741367</v>
+        <v>0.1761911799899869</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0673567633634863</v>
+        <v>-0.03827472310626492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01859211617710081</v>
+        <v>-0.00523864866228527</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1469424892437396</v>
+        <v>0.1484727551583226</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1916030129141663</v>
+        <v>0.0527932376933186</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1110782829827136</v>
+        <v>-0.08968575381093824</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01574459637430184</v>
+        <v>0.04256537961630154</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.006316789947260585</v>
+        <v>-0.03527698599165558</v>
       </c>
       <c r="R2" t="n">
-        <v>0.178454042786624</v>
+        <v>-0.1366488185341298</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.05327397851838588</v>
+        <v>0.1101047453665887</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03807073222906859</v>
+        <v>-0.01426126101579678</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1758603176102459</v>
+        <v>-0.1034046340873072</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1183554032406922</v>
+        <v>0.2161472145921148</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002314544606478837</v>
+        <v>-1.997388889301581e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1007139419984857</v>
+        <v>0.2017224237550338</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08177401583148758</v>
+        <v>-0.1288822817886972</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.0394637560088557</v>
+        <v>-0.04016342506501856</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04630725137966091</v>
+        <v>-0.1060471679706807</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1021241990320885</v>
+        <v>-0.1402813994548196</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1458202046875087</v>
+        <v>0.03310468100259829</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.02355893832512629</v>
+        <v>-0.094987652320683</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.2078974225353832</v>
+        <v>-0.1690551139902161</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.130677332122027</v>
+        <v>-1.621016987363925e-06</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.04376340524988363</v>
+        <v>0.2433639776880481</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1231410246920658</v>
+        <v>-0.108086731888861</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0005249951159391069</v>
+        <v>-0.2656236520975216</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.07713051534808042</v>
+        <v>0.1400439348665012</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02626992237207834</v>
+        <v>-0.003916926027008378</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.02695184344177427</v>
+        <v>0.1377974976116436</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.1016494066592592</v>
+        <v>0.1007132702329158</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.01751263728412372</v>
+        <v>-0.007472898324901579</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1115800187178002</v>
+        <v>0.02719151953293126</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.2427107910249345</v>
+        <v>-0.1388608099396459</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.05000115091311568</v>
+        <v>-0.08863176622278321</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.1059527423540017</v>
+        <v>0.1018430545545164</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.2453834916586427</v>
+        <v>0.1644992552330047</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0001542930890584172</v>
+        <v>0.1736501676608874</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.05924352036121923</v>
+        <v>-0.1160293384292986</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2057972724393518</v>
+        <v>-0.009430784731490742</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.006984593327784948</v>
+        <v>-0.008993722786702959</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.003719819511727282</v>
+        <v>0.1242784901581851</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.02830289187765056</v>
+        <v>0.2251960867329606</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1232189629747345</v>
+        <v>-0.1731927160686202</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.1154265794312637</v>
+        <v>-0.1028913847271289</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1018480217712891</v>
+        <v>0.002670637514252762</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.023774041338205e-05</v>
+        <v>0.1515771004553803</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.2007940469817002</v>
+        <v>-9.913132257329542e-09</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.03737359173150086</v>
+        <v>0.1308438719879876</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.03016874797663875</v>
+        <v>-0.01029171418701422</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1674489457536177</v>
+        <v>0.2228246529981212</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.05794900912564504</v>
+        <v>0.06058916511699474</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.1204826939194294</v>
+        <v>-0.1529898484803646</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1613029023758395</v>
+        <v>-0.06129104843490263</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.02231561602913743</v>
+        <v>4.033335702974167e-05</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.02747969567535952</v>
+        <v>-0.06661479847933295</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.0728103882218009</v>
+        <v>-0.03924541782463363</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.2176586405973596</v>
+        <v>-0.173118116026022</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01550604145475405</v>
+        <v>0.08530586150452198</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.04698364910756438</v>
+        <v>-0.0615081031098924</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.2489536778729002</v>
+        <v>0.1344969546832491</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.050105124938032</v>
+        <v>5.826456748789595e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1167957383565914</v>
+        <v>-0.1492434284077808</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.08399965746863329</v>
+        <v>-0.127925894276664</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.2251544221835248</v>
+        <v>0.001128227245495157</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.02648542370846593</v>
+        <v>-0.1351827438090312</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.07922236846332031</v>
+        <v>0.1351409656096133</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04683194868380562</v>
+        <v>0.2333073263721392</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.09662781146644039</v>
+        <v>-0.2536477938900255</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.09395230156385892</v>
+        <v>-1.033248778689541e-08</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1079587234858431</v>
+        <v>-0.02257754882222674</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.1577888063116089</v>
+        <v>-0.08416688486515081</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.03347678961870954</v>
+        <v>0.04593749494284263</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.1233798106888512</v>
+        <v>-0.07700452030847491</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.04333966807613053</v>
+        <v>-0.07621303244146833</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.0739189974545383</v>
+        <v>0.02413040420030137</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.1074080879339515</v>
+        <v>-0.1355396864478255</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.073634141512589</v>
+        <v>0.08525971009593299</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.04304001320690418</v>
+        <v>0.1152040412155416</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.109835610384493</v>
+        <v>0.05687836702744568</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1267011387495757</v>
+        <v>2.749373576461245e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1299061478197307</v>
+        <v>-0.0156753272210684</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1001392336904723</v>
+        <v>-0.2252360197787964</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.07955350485608809</v>
+        <v>-0.1642627802217396</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.09275281549841659</v>
+        <v>-0.1691043714176356</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.006948498004167361</v>
+        <v>-0.0334885445277323</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.1514798124814044</v>
+        <v>-0.1143771007444344</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.00688387402410257</v>
+        <v>-0.01908061434731458</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.09982375477388687</v>
+        <v>-0.1289095655517519</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.1285551442235661</v>
+        <v>0.167275274074208</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.09287046649326254</v>
+        <v>-0.06739197844697238</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.01228135369972552</v>
+        <v>-0.006589347229658409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2413952931974666</v>
+        <v>-0.04682724454308347</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0007272847303655061</v>
+        <v>0.1017586654962834</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04734157472287915</v>
+        <v>0.1600432880709577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1985783031412945</v>
+        <v>-0.04226062398012308</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1244014108084694</v>
+        <v>-0.06289911681746127</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1923204838454803</v>
+        <v>-0.1027454047689548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1594518292501265</v>
+        <v>-0.2052690541346496</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.215965169142651</v>
+        <v>0.08763687972563783</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1209091010926581</v>
+        <v>-0.01225007957546454</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1452914017994</v>
+        <v>0.2272613300791071</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.11214410002908</v>
+        <v>-7.101126898797931e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2146534180147024</v>
+        <v>-0.2464395691653463</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02721250526259281</v>
+        <v>-0.1525689587296899</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0777832003782393</v>
+        <v>-0.001709827699722147</v>
       </c>
       <c r="O3" t="n">
-        <v>1.436248604509836e-05</v>
+        <v>-0.1436806528712517</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.03239579255493744</v>
+        <v>-0.1155121932764212</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1964130791100469</v>
+        <v>-0.2047352917254028</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0006488254156385921</v>
+        <v>-0.008432649259018002</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1087378835181618</v>
+        <v>0.1045289576465136</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1921084473059164</v>
+        <v>-0.1987405757828508</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05940840608565121</v>
+        <v>0.09037598341479285</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.01396340219474721</v>
+        <v>-0.1080098276107246</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.05950018976687241</v>
+        <v>1.647908348228906e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1162653637210322</v>
+        <v>-0.1557039795400068</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.02912667787640525</v>
+        <v>0.1168712719899132</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1850427076990078</v>
+        <v>-0.0606787096986765</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.1195422582577109</v>
+        <v>0.07451886649788701</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1056351708190942</v>
+        <v>-0.02351820898044103</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1846423655655838</v>
+        <v>-0.04313235703478555</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.1416098021449712</v>
+        <v>0.1823451708930453</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.193511180485926</v>
+        <v>-0.05406981733426161</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02476542617350473</v>
+        <v>0.01233664823133281</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.1377911482630401</v>
+        <v>-0.09917511289253544</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2.316494621847061e-06</v>
+        <v>0.2263101363105407</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09441327785375075</v>
+        <v>-0.05519140058625813</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.003768780067026121</v>
+        <v>0.2341733544704873</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.2033397082879621</v>
+        <v>-0.1074600182759578</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.1801250836583723</v>
+        <v>0.09480129932237345</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.04222853229569667</v>
+        <v>-0.1870887503768149</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.01981613880527106</v>
+        <v>0.03190973078133068</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.02133188980564286</v>
+        <v>0.06101091500793635</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2046356858311762</v>
+        <v>-0.07670541068768655</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.00941965645794765</v>
+        <v>-0.090968161927955</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.2198038613145837</v>
+        <v>0.0663445604455308</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1436404474620546</v>
+        <v>0.1214983890418074</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.000492372735154361</v>
+        <v>0.138982375254483</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1097675451504837</v>
+        <v>0.084392720542142</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.1801952326041966</v>
+        <v>-0.02101626190344666</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.1053661782953221</v>
+        <v>-0.007702583747350359</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1820240716163141</v>
+        <v>0.0201684576935424</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.1174440081346958</v>
+        <v>-0.03607882665040055</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1738836785853622</v>
+        <v>0.02966663371258675</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1543135340962385</v>
+        <v>0.1948577281092783</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.006775118112334685</v>
+        <v>9.618952038538859e-09</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.02343701724155176</v>
+        <v>0.1309164524175059</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1233496247218267</v>
+        <v>-0.02076292199451747</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.05215830135121734</v>
+        <v>-0.1287959967578112</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.009372402676213006</v>
+        <v>0.1466483693166757</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02903444731219474</v>
+        <v>0.01385356256400149</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.03871367396170984</v>
+        <v>-0.08198355680077672</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.02649291662863867</v>
+        <v>0.01580848947423682</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.04722720759986174</v>
+        <v>0.1137732127842656</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1749413167406775</v>
+        <v>-1.212216654719636e-09</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.03491081946313752</v>
+        <v>0.09534279682589948</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.02944791617668045</v>
+        <v>-0.09170752422908746</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01209121009223257</v>
+        <v>-0.009911477371886216</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.09513721857640832</v>
+        <v>0.2091279492353535</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.196655045590397</v>
+        <v>-0.1724193324204271</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.174955483111418</v>
+        <v>0.07236956947598389</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.03597568099242371</v>
+        <v>-0.1541702871583092</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.223999707045659</v>
+        <v>0.1411322378637232</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.07679129104377186</v>
+        <v>0.09977923384169307</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.07563684196881269</v>
+        <v>-0.1112909359898204</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0653936967104536</v>
+        <v>0.09197433229158171</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2112349633649015</v>
+        <v>-0.06283081447986907</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.002949876234078962</v>
+        <v>0.193117816028748</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.02635315351893631</v>
+        <v>0.05092546840164882</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1649257313803912</v>
+        <v>-0.01298862698441787</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.1766945655086288</v>
+        <v>-0.03754782387918783</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1443410767290657</v>
+        <v>-0.02050543754841515</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.196965809003377</v>
+        <v>-0.0415907608009557</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.1200909001233068</v>
+        <v>0.1731255965559968</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.08149392209504275</v>
+        <v>0.05661028496182614</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.2188585208170198</v>
+        <v>0.1099820946800329</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.1193230331675897</v>
+        <v>-0.1033734549436846</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.02617395229647053</v>
+        <v>0.197144576751276</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.1883697172838435</v>
+        <v>0.1697487028678285</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1817582668134557</v>
+        <v>0.1365278979640589</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.2060716542523809</v>
+        <v>-0.0001769900386338166</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1593389668953724</v>
+        <v>-0.03481465136313189</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.07474414963110593</v>
+        <v>0.1368221932460633</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.03076441686132975</v>
+        <v>-0.1401799823768999</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.1288093723360188</v>
+        <v>0.1557135230198591</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.02286469420585365</v>
+        <v>-0.03037979526494789</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1215421771488854</v>
+        <v>-0.2274142685743105</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.02194758761943003</v>
+        <v>-0.2144331449702965</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.02555217057853949</v>
+        <v>0.02453816353764758</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0115732113511161</v>
+        <v>-0.03316730017631459</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.09671574316269661</v>
+        <v>0.1184531921454824</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0432172505707083</v>
+        <v>-0.008313864190585215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.142453354463209</v>
+        <v>-0.001819811723039797</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1099156887051409</v>
+        <v>0.04243171153062197</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09615942120785732</v>
+        <v>-0.1537150261675052</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07350089091530389</v>
+        <v>0.1320284964633957</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0002232590793418531</v>
+        <v>0.1288202079022117</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06947960426977624</v>
+        <v>0.2639016648123679</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1380801564988187</v>
+        <v>0.1345998671151404</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05828437477645953</v>
+        <v>-0.2352417417018462</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1139755916202918</v>
+        <v>0.1587553484215793</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2085847825319946</v>
+        <v>-0.02616680728496827</v>
       </c>
       <c r="K4" t="n">
-        <v>0.131964503626235</v>
+        <v>-0.0007782997333173548</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1294959106691239</v>
+        <v>0.1119420281070519</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.006123717767882834</v>
+        <v>0.1182198219850418</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.08891885988496556</v>
+        <v>-0.009563308303642711</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06838572798643341</v>
+        <v>0.1506792715582653</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.09121318915216771</v>
+        <v>0.04644953599841726</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1892696008342807</v>
+        <v>0.04496219939754925</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1508537178522268</v>
+        <v>-0.07548154353297877</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1888813684690637</v>
+        <v>-0.09919773492951924</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1768722354106719</v>
+        <v>0.1101123319634775</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1393825801333634</v>
+        <v>-0.2081235463480192</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.08819486082374101</v>
+        <v>0.01834956122295129</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.05052003571831487</v>
+        <v>-0.004032955473557346</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2182067283425804</v>
+        <v>0.05163715971485908</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.002604586665320554</v>
+        <v>0.02489690261288326</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06967624166026125</v>
+        <v>0.02933509331105792</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.03201896574055856</v>
+        <v>0.1856677875203794</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07615289184056255</v>
+        <v>0.2344826578976918</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1162105378588452</v>
+        <v>0.005599689475984121</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1266103248183638</v>
+        <v>0.113724721876053</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.1167663062407043</v>
+        <v>-0.04113966692641148</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.06651854835394314</v>
+        <v>-0.1755505077848753</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.144414946644368</v>
+        <v>-2.406342446297031e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.02116664282616083</v>
+        <v>0.01796326951459318</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1551362056564753</v>
+        <v>-0.1046179034266558</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.06832064581669052</v>
+        <v>-0.1251266243903299</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2407174744565285</v>
+        <v>0.1368449622964114</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08926899603852738</v>
+        <v>0.06536683364606242</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2546666564112029</v>
+        <v>0.04207151527471861</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1404226589754693</v>
+        <v>0.1274442293011581</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01891926341632147</v>
+        <v>0.1405502910211424</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1560706914350465</v>
+        <v>-0.1214853019661278</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.06194211863295583</v>
+        <v>0.1529741412386412</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1378885795275923</v>
+        <v>-0.08405846951167711</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.02740377183445277</v>
+        <v>0.004042426552586871</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.08862573377994717</v>
+        <v>-0.1382777836558532</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.08579790075800986</v>
+        <v>-0.06175451644145356</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2120233547811152</v>
+        <v>-2.069896425433612e-07</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.01767996807191046</v>
+        <v>-0.0101467987463347</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1284295811868583</v>
+        <v>-0.2013555325691086</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.117682187246209</v>
+        <v>-0.08798344655872636</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1210405363511782</v>
+        <v>-0.1729250912268497</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2200548584728563</v>
+        <v>-0.2148125078405927</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.07148274096041463</v>
+        <v>-0.0447400950787436</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.003494424795588218</v>
+        <v>-0.09729990970899208</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.07909770985421845</v>
+        <v>-0.009009202772662915</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.02266705277237226</v>
+        <v>0.004990887469322379</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1062120361732347</v>
+        <v>0.1899993542103844</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.2257669161316275</v>
+        <v>0.2327707130823255</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.03976237892383089</v>
+        <v>0.09903355491548198</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.09943994889972634</v>
+        <v>-0.07474311338735699</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.2238594487117017</v>
+        <v>-0.01767403606388226</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1258666533881992</v>
+        <v>-0.01092654404979367</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.1744382619284514</v>
+        <v>-0.161415264714486</v>
       </c>
       <c r="BM4" t="n">
-        <v>-8.36091879180333e-07</v>
+        <v>-0.1334519842298938</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0.05645426805187735</v>
+        <v>0.08657095617214065</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.08785074832340763</v>
+        <v>-0.1907524908986084</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.1726813904865517</v>
+        <v>0.2024063315732208</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.244897172606865</v>
+        <v>0.1830247051036845</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.187018453887358</v>
+        <v>-0.1948854954324951</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1205119207774365</v>
+        <v>0.1372925489559737</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.08343717702987341</v>
+        <v>0.2297077685486902</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.04899086489588974</v>
+        <v>0.186141062494706</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2057182848499734</v>
+        <v>-0.06443713980637437</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.171708432339698</v>
+        <v>0.0007032829088813728</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.007578947306995909</v>
+        <v>-0.1063338714996134</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1872979203858117</v>
+        <v>0.22795059085532</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.01564185226412145</v>
+        <v>-0.1808643091986639</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.135045437910221</v>
+        <v>-9.485421114598563e-08</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.02677063206562924</v>
+        <v>0.1506582724629889</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1134373175556764</v>
+        <v>0.006660953796580063</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.07056080697532267</v>
+        <v>0.1508846140915552</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0233288342247261</v>
+        <v>-0.0273909349922541</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0.1005048044032981</v>
+        <v>0.2065978586568363</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.006520868619628781</v>
+        <v>0.1965344706631239</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02866936877040388</v>
+        <v>-0.1001993519472446</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.0737082149330653</v>
+        <v>0.01074125086667144</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.03845621884179094</v>
+        <v>-0.1487349241334187</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.07961621946431888</v>
+        <v>-0.009912223907832812</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.1629416383403399</v>
+        <v>-0.005589472511977151</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.111521523752145</v>
+        <v>0.1806961522366946</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.07019424639329544</v>
+        <v>0.08753462712910873</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1763068398194647</v>
+        <v>-0.01357752939242384</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.007930429302355423</v>
+        <v>-0.002501722841564765</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1376334379699952</v>
+        <v>-0.04340186294348093</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.009283400227202542</v>
+        <v>0.009583372565821004</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.09659655740990984</v>
+        <v>-0.04090029352077125</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0.06965293412069222</v>
+        <v>-0.1032037882827082</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.2222121375504979</v>
+        <v>-0.2201309112553492</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.01384090033203071</v>
+        <v>-0.2272347492382193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1361157188518375</v>
+        <v>0.0001759867056900877</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0001019957605593627</v>
+        <v>0.07901510250353534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2077384444674999</v>
+        <v>0.08138586910585886</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06850479726477816</v>
+        <v>-0.02363399948357615</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01898189954906079</v>
+        <v>0.06624355887354805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132544435379679</v>
+        <v>-0.1225738621775418</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05919669670234564</v>
+        <v>-0.1401102659259593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1342999580842771</v>
+        <v>0.1249392701341933</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1632057113914009</v>
+        <v>-0.05018896360102227</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1682834986062694</v>
+        <v>0.1408305608799448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05902121073110676</v>
+        <v>-0.01894026077657824</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1097788722230109</v>
+        <v>0.1729247025323335</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2440887596165592</v>
+        <v>-0.005275918775016869</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08634817431926436</v>
+        <v>-0.04549077596457494</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.07344957058579299</v>
+        <v>0.001100657158598837</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0003020894014386281</v>
+        <v>-0.007255434046239386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1971216750473679</v>
+        <v>-0.006421230952134827</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1640933810015468</v>
+        <v>0.01335464832636117</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1290167133476586</v>
+        <v>-0.004878590319608957</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1066382824680625</v>
+        <v>-0.2189128043211633</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06489850138484295</v>
+        <v>0.1018363022393196</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1260600940546143</v>
+        <v>0.07425271953175962</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.001628726736338265</v>
+        <v>-0.01183012297752167</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.06623284673937818</v>
+        <v>0.001315514440729913</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.124115390973449</v>
+        <v>-0.1798491301986691</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03450539108609788</v>
+        <v>0.07000276642602679</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002637065183642222</v>
+        <v>0.09294249585364141</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002613662696703659</v>
+        <v>0.02650453251690127</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0993512882007353</v>
+        <v>0.004741729760621292</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2272666480698855</v>
+        <v>0.2138316554035547</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01444262551661058</v>
+        <v>-0.01448399655076016</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02084396538229245</v>
+        <v>0.2113901820116893</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.1161130676042686</v>
+        <v>-0.05570842174092407</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.04768646712170437</v>
+        <v>0.0916736772834176</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1245764707513159</v>
+        <v>0.1406888924148531</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1516015249581898</v>
+        <v>-0.05833411877350661</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.2417044020677474</v>
+        <v>0.1120771110883353</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.2110172578391361</v>
+        <v>0.1284960230430666</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.08621617395145983</v>
+        <v>-0.1581270112321968</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.1922048820726282</v>
+        <v>0.1893857810520408</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1215235326746915</v>
+        <v>-0.04999417852032763</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.06349098997627947</v>
+        <v>0.1307654786644313</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.005184684196008638</v>
+        <v>-0.1111540864966672</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1048523912996279</v>
+        <v>0.1202616185121186</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.008233357107557699</v>
+        <v>0.1822814569816207</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.446691201197367e-05</v>
+        <v>-0.1031024539980704</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2063873811965163</v>
+        <v>-0.004815511230843036</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2443460426391759</v>
+        <v>-0.002271308158908677</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1037434383596235</v>
+        <v>0.005354345447792838</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0114249469782372</v>
+        <v>0.1277016927539518</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.01329484474553737</v>
+        <v>0.03459796965765281</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.17814167739248</v>
+        <v>-0.145827583454798</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.2464478668583145</v>
+        <v>-0.07766444851300888</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.2192749882953168</v>
+        <v>1.945540970166781e-05</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.04160307345228356</v>
+        <v>-0.06477899932918274</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.08446748737625369</v>
+        <v>-0.04414861487852892</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.139355451237806</v>
+        <v>0.05522266488437085</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01449237774077976</v>
+        <v>-0.08656248058212225</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.111754438246424</v>
+        <v>-0.09324057257590498</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1241961030202866</v>
+        <v>0.1150846296306748</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.09011227191067257</v>
+        <v>0.05816995324537836</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002942884377870269</v>
+        <v>0.08262262324690055</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.202922036915568</v>
+        <v>-1.368138326586885e-07</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.08035741816898849</v>
+        <v>0.07083749489224021</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.06141889072132212</v>
+        <v>0.171763629577571</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1582006645170096</v>
+        <v>-0.03097305939364584</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1304266738452905</v>
+        <v>-0.1505147674605223</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2409380783130067</v>
+        <v>-0.2461446247586346</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.01514281039618009</v>
+        <v>0.1497144797721077</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.1881116453352279</v>
+        <v>0.02262014438826881</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1451398875590292</v>
+        <v>-0.2275524046515297</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0861423189901751</v>
+        <v>-0.08410719225549479</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1294843337059318</v>
+        <v>0.1440509655951012</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.128152412081362</v>
+        <v>-0.02698781152693858</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.02739865992581813</v>
+        <v>0.1255661825148008</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.2285005724222054</v>
+        <v>0.2352441647001732</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.2282350551174712</v>
+        <v>-0.2014090919903284</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.2101736513679894</v>
+        <v>0.1968188313606157</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.02545005933967012</v>
+        <v>-0.03468564992728689</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.01496552123067697</v>
+        <v>-0.2068791957595782</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.2502127550464998</v>
+        <v>0.00325633912640034</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.09479901978356896</v>
+        <v>0.009425748569813501</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.04423599394897833</v>
+        <v>0.1282547428148668</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.2184061589390281</v>
+        <v>0.07804239839447859</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1267701722770685</v>
+        <v>0.06189199008669719</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.1309092449498487</v>
+        <v>0.2399926249133533</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1822536210313227</v>
+        <v>-0.05559811626234558</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.17790241278125</v>
+        <v>-0.01663988276224381</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.2268342849956418</v>
+        <v>0.009554814728817428</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.173032578586914</v>
+        <v>-0.04214736187459611</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.008630057330209549</v>
+        <v>0.0309209622701336</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04676660158663019</v>
+        <v>0.02483044271784174</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1485194157504702</v>
+        <v>0.06217018729988152</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.09112245376775169</v>
+        <v>0.02612286334567044</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1623777771093561</v>
+        <v>0.08098197475777427</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.09807723257600516</v>
+        <v>-0.02607984894913983</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.07569666097702203</v>
+        <v>0.04433384116549136</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.03725604847034509</v>
+        <v>0.1300733875593457</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.1695211742049113</v>
+        <v>-0.01698919522581877</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.06651685773049024</v>
+        <v>-0.01163334018428189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.006240892045355562</v>
+        <v>0.0001355542168081236</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0003451138501616207</v>
+        <v>-0.2232197048460878</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.05846737393132122</v>
+        <v>0.1621986182657565</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08556936396412033</v>
+        <v>-0.2105010274181476</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07294587441620703</v>
+        <v>-0.179830667487804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2180642086982937</v>
+        <v>-0.1601779621974382</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08421162973541847</v>
+        <v>0.1694903589690197</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1412899499474544</v>
+        <v>-0.09543277232336246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1026302674444111</v>
+        <v>0.08093985090006293</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1621537298708889</v>
+        <v>0.04812164031620415</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.09067485830760942</v>
+        <v>-0.01108704963913727</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0558567849554406</v>
+        <v>-0.04607839930570432</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02585903326253416</v>
+        <v>-0.08917780406270449</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1394632460622994</v>
+        <v>-1.923617344483725e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002356304869388284</v>
+        <v>-0.2130126398658778</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.001319186547986263</v>
+        <v>-0.1967079603683003</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0574831165716464</v>
+        <v>-0.02519010474426222</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1283541489099372</v>
+        <v>0.1185760506038663</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1041013092343669</v>
+        <v>-0.05564954032147969</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.02924193053748227</v>
+        <v>0.1936890652951836</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.162348850669317</v>
+        <v>0.01243761436089176</v>
       </c>
       <c r="V6" t="n">
-        <v>5.685249819998286e-06</v>
+        <v>-0.2466712186016666</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1098006901830353</v>
+        <v>-1.387316113505296e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1750514550171406</v>
+        <v>-0.1262071376167893</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1195474232136388</v>
+        <v>0.1048924397086013</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0103721493826118</v>
+        <v>0.2212252551298555</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.07503583215420551</v>
+        <v>0.09879671677009505</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1101995987206786</v>
+        <v>0.1164257915805503</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01928294054107571</v>
+        <v>-0.002480383877786069</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0869520779142396</v>
+        <v>0.09705970729979545</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2183744136493732</v>
+        <v>0.1105355809136516</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01991216165415454</v>
+        <v>-0.06487162757477224</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1201043577274704</v>
+        <v>0.1831532767912057</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.03827266983823407</v>
+        <v>0.1794718010487185</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2333146460216348</v>
+        <v>0.1406141775579406</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09654725413516729</v>
+        <v>-0.02901982585819247</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1961845448778349</v>
+        <v>0.1488015541761786</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.06475839130973056</v>
+        <v>-0.1216590414483477</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.08228004977133965</v>
+        <v>0.2229979934973681</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.115961755248247</v>
+        <v>0.07708101012352447</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.1039271453238811</v>
+        <v>-0.03733364215096276</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.01583580249289785</v>
+        <v>0.1099956970091424</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.05654035729477759</v>
+        <v>0.05011280138485784</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.09146082906925386</v>
+        <v>0.07273379670544437</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2348242584864058</v>
+        <v>0.07515277397244881</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.07626334433556563</v>
+        <v>0.08303500595718129</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.02383676364244334</v>
+        <v>0.2383673590096551</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.04139995513088328</v>
+        <v>-0.03606466796626987</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.005892405433521675</v>
+        <v>3.252127704705398e-08</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.02922551570226636</v>
+        <v>0.02096922203486851</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.02398355370635331</v>
+        <v>0.07110671889142244</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01212564641553114</v>
+        <v>0.1699745484628909</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.05946705025789551</v>
+        <v>0.2058666721151231</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.17515578186343</v>
+        <v>-4.505128284018626e-05</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.03661967947969598</v>
+        <v>-0.095314772802155</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.07674009479511847</v>
+        <v>-0.003323556724375361</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.1470029866925688</v>
+        <v>0.01296927423038381</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1663041066538782</v>
+        <v>0.1602001547615332</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1885256808571456</v>
+        <v>-0.02556589716249271</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.03214644542525912</v>
+        <v>0.2173930914882428</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.1009469141588248</v>
+        <v>0.1940182010969766</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.1365665224472098</v>
+        <v>-0.08799334438420638</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.01664673513273315</v>
+        <v>-0.01249023783771295</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.03345486430414576</v>
+        <v>0.1615555286836603</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0961265746318002</v>
+        <v>0.2138944585369806</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.1628405169317243</v>
+        <v>-0.08309119355195051</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.1813947228255312</v>
+        <v>0.06305654133678661</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.09748635497023861</v>
+        <v>-0.1246946455597431</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.2044336970193356</v>
+        <v>0.1039545628716166</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.2302563997727333</v>
+        <v>0.1714826206060646</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.1253408983957321</v>
+        <v>-0.03671517987140906</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.03088565068781423</v>
+        <v>0.2056092798479409</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.1670846170396304</v>
+        <v>-0.04063151122873664</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.09329198544259411</v>
+        <v>-0.08347431052175906</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1547402700435385</v>
+        <v>-0.1816777532394666</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.06190357107106241</v>
+        <v>0.02795356009208404</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.2242944300024786</v>
+        <v>0.03690538990462513</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.2240436155332787</v>
+        <v>-0.02248693619302324</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02892853920074518</v>
+        <v>-0.01341457051651808</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.001256002838011201</v>
+        <v>-0.1804853282572641</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.1148300648930835</v>
+        <v>0.001335357023918836</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.09341348480015431</v>
+        <v>-0.1316905629471002</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.03222735525075174</v>
+        <v>0.02020709266278066</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.05338883877497648</v>
+        <v>-0.09023542728545032</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1234605127462324</v>
+        <v>0.1780510417126419</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.2446406341955429</v>
+        <v>0.1058375687782623</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1796320980346844</v>
+        <v>-0.1193129236007349</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.04628970385793001</v>
+        <v>-0.03964517073103899</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.1594478019468034</v>
+        <v>-0.05380932340243494</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.04885136045103941</v>
+        <v>-0.02320390013199751</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.07406273587161168</v>
+        <v>-0.1682005953975514</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.05331970794494567</v>
+        <v>0.05874479829892044</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1513552743478699</v>
+        <v>0.01438589308368313</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0001184105863254286</v>
+        <v>-0.01893227956810737</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1994365601666291</v>
+        <v>0.2161163882987807</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.05099462076434234</v>
+        <v>-0.06800457521968351</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.00430356830744289</v>
+        <v>0.06366901481197208</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.00156666716388089</v>
+        <v>0.1254455468674224</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.02602766294792224</v>
+        <v>-0.06847157010893826</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.03042442504616875</v>
+        <v>0.04730109265214471</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1381370831242464</v>
+        <v>-0.05235068697337936</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.001501870027146861</v>
+        <v>0.01248623651401232</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1466580665861645</v>
+        <v>-0.0799842237494594</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08911456348150691</v>
+        <v>0.1955287575151147</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05275543643241383</v>
+        <v>-0.1493778376010789</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06389038073575287</v>
+        <v>0.2651613629450593</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.007615352946495371</v>
+        <v>-0.1306669979827538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.226427503290503</v>
+        <v>-0.09077782344781131</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03341050519625569</v>
+        <v>0.2879120972544238</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.06869782328794624</v>
+        <v>-0.06068913614571898</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008032980570541285</v>
+        <v>-0.0145876716120496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06994028339526943</v>
+        <v>0.1580186877258653</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08160547723437317</v>
+        <v>0.09006372317558525</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03564083969658108</v>
+        <v>-0.03399021988094608</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07421212419150305</v>
+        <v>-0.0877851431277607</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1034992235598471</v>
+        <v>-6.749342675984093e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2423349653398177</v>
+        <v>0.0003830446009412988</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1605227560384187</v>
+        <v>0.08536128349759418</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1631142463469935</v>
+        <v>0.1110100898205196</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2088498900333802</v>
+        <v>0.1259710107386707</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04043116261452476</v>
+        <v>-0.1244145334328686</v>
       </c>
       <c r="V7" t="n">
-        <v>0.07128867556298402</v>
+        <v>0.004144859598992745</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009431418989349441</v>
+        <v>0.02148781675424508</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1043084455383352</v>
+        <v>-8.328859911609379e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0279453450515104</v>
+        <v>-0.2325167753686226</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.130726635142719</v>
+        <v>0.2316560806963688</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.03090762472805387</v>
+        <v>0.02174999706256894</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05638218604254575</v>
+        <v>0.1166646216475104</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0553760113946276</v>
+        <v>-0.0002514371602142248</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.2069778814993569</v>
+        <v>0.1152383201073488</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1349727812213321</v>
+        <v>0.1276401177582209</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1343263382245559</v>
+        <v>0.07124377447466698</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04410573490814121</v>
+        <v>0.2108449939158397</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.02112301553524352</v>
+        <v>-0.1342777303311771</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.04816873837663363</v>
+        <v>-0.1649904808864916</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09393078268884335</v>
+        <v>-0.08687388636546137</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09372349383749126</v>
+        <v>0.1990897446757212</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.08527423394410859</v>
+        <v>0.2154513475850459</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.07364483882969883</v>
+        <v>0.1059339734144657</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2320896903482425</v>
+        <v>0.1161171145247481</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0004720186169337314</v>
+        <v>-0.1234182113060785</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.169222872823061</v>
+        <v>0.1210911559049662</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.04563351608493135</v>
+        <v>-0.02987266070335852</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.06815631750687473</v>
+        <v>-0.2390738009348743</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1408112554516583</v>
+        <v>-0.0915310227037523</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.01785465699468268</v>
+        <v>-0.2115208980932344</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1649742015820245</v>
+        <v>0.2464024576069417</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.02254399619538603</v>
+        <v>1.105488706090586e-09</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1081120647027511</v>
+        <v>-3.863259448890296e-05</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.2241727171594479</v>
+        <v>-0.2170922406437102</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.00529584132684268</v>
+        <v>0.01869979877676926</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.1959494050571841</v>
+        <v>0.2007843034648459</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.1878826156112034</v>
+        <v>0.09471201255349344</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.07062997910641355</v>
+        <v>-0.001374279599651618</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.02414166401982852</v>
+        <v>-0.06600392737518058</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.07380139344644461</v>
+        <v>0.007147505810669248</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1617097760900207</v>
+        <v>0.2000251612718211</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04414883694791666</v>
+        <v>0.1761844824268124</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1983918701814464</v>
+        <v>-0.2130447323273859</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.007646041786635422</v>
+        <v>-0.1217887885370826</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.02620910670322654</v>
+        <v>-0.07549182715300484</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.1538252984750627</v>
+        <v>0.0946242620270256</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.03843204643067068</v>
+        <v>-0.01936459446141201</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.06066642923310407</v>
+        <v>0.1753691185114184</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.09962899228525038</v>
+        <v>0.08884730369598666</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.2174003237249882</v>
+        <v>-0.2119148863003882</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.07131937061583221</v>
+        <v>0.05293044173208709</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.1408680748282526</v>
+        <v>-0.1603767501489385</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1079059818249981</v>
+        <v>0.022084316861575</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.03162549581689628</v>
+        <v>-0.01995683525407371</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.001918656896558472</v>
+        <v>0.02741155686853818</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.192738841067093</v>
+        <v>-0.04815855284393827</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003839835181892055</v>
+        <v>-0.02586754239405547</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1509940593321022</v>
+        <v>-0.04244317320241004</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.02174516619482771</v>
+        <v>-1.905467700529948e-07</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.1565115488974462</v>
+        <v>0.04836482639847016</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.233543686022493</v>
+        <v>0.06619016208473615</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.2203469431982842</v>
+        <v>-0.1364635704691657</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.05089413871576754</v>
+        <v>9.072163965472468e-07</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.05565027319702965</v>
+        <v>-0.0285065049081073</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.002273294282384027</v>
+        <v>8.165649596655629e-07</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.2106659270329126</v>
+        <v>0.05254130111656999</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01817411686662188</v>
+        <v>-0.08998324025227655</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.1218282141582196</v>
+        <v>0.1864869153066759</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.2101778621076606</v>
+        <v>0.005146588032678496</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0579205423730872</v>
+        <v>-0.06188617976060262</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03223479410862651</v>
+        <v>-0.2320301079387196</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.05058982868307143</v>
+        <v>0.05602859720051166</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.05511614980910159</v>
+        <v>-0.01436065185771154</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.05874886077057042</v>
+        <v>-0.02285769856931923</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1185662275885931</v>
+        <v>0.0385888607389491</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.1764089448367635</v>
+        <v>0.02531356554427807</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.2217058318046127</v>
+        <v>-0.2281647253594975</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.007118730588992476</v>
+        <v>0.03697708118973191</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001504087071130237</v>
+        <v>-0.07221462109541121</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.01772736280079639</v>
+        <v>0.004985690955999503</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1786638929289368</v>
+        <v>-0.07068672027930804</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.002837534394789219</v>
+        <v>0.231563967261218</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.09454896175739637</v>
+        <v>0.1790563043444776</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.05947936732606422</v>
+        <v>-0.05504382545547491</v>
       </c>
     </row>
   </sheetData>
